--- a/simulations/scene/inputs/Scenarios_24_11_10.xlsx
+++ b/simulations/scene/inputs/Scenarios_24_11_10.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TIGERA~1\AppData\Local\Temp\scp45367\home\torisuten\package\Wheat-BRIDGES\Root_BRIDGES\simulations\inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TIGERA~1\AppData\Local\Temp\scp23692\home\torisuten\package\Wheat-BRIDGES\Root_BRIDGES\simulations\scene\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7937E954-3C86-445D-9E19-5F7F09E14CE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A99BDFC-FDC9-4F97-A323-27A18616A78E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28830" yWindow="-19695" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="scenarios_as_columns" sheetId="2" r:id="rId1"/>
@@ -14831,11 +14831,11 @@
       </c>
       <c r="L135" s="83"/>
       <c r="M135" s="83">
+        <f>0.0005 * 1.5</f>
+        <v>7.5000000000000002E-4</v>
+      </c>
+      <c r="N135" s="83">
         <f t="shared" ref="M135:W135" si="60">0.0005 / 10</f>
-        <v>5.0000000000000002E-5</v>
-      </c>
-      <c r="N135" s="83">
-        <f t="shared" si="60"/>
         <v>5.0000000000000002E-5</v>
       </c>
       <c r="O135" s="83">

--- a/simulations/scene/inputs/Scenarios_24_11_10.xlsx
+++ b/simulations/scene/inputs/Scenarios_24_11_10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TIGERA~1\AppData\Local\Temp\scp23692\home\torisuten\package\Wheat-BRIDGES\Root_BRIDGES\simulations\scene\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6B2AF53-4997-415D-A854-9921685F5463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4151DA82-33A1-43F4-BF38-7AB35356AC49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/simulations/scene/inputs/Scenarios_24_11_10.xlsx
+++ b/simulations/scene/inputs/Scenarios_24_11_10.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TIGERA~1\AppData\Local\Temp\scp23692\home\torisuten\package\Wheat-BRIDGES\Root_BRIDGES\simulations\scene\inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TIGERA~1\AppData\Local\Temp\scp16920\home\torisuten\package\Wheat-BRIDGES\Root_BRIDGES\simulations\scene\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4151DA82-33A1-43F4-BF38-7AB35356AC49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DC8005E-FC92-4DCF-8E4E-8FF6E48B0BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2488,7 +2488,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2696,6 +2696,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="11" fontId="16" fillId="51" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -23003,16 +23004,16 @@
         <v>5.0000000000000002E-11</v>
       </c>
       <c r="L221" s="83"/>
-      <c r="M221" s="83">
+      <c r="M221" s="101">
+        <f>0.00000000005 * 2</f>
+        <v>1E-10</v>
+      </c>
+      <c r="N221" s="101">
+        <f>0.00000000005 * 2</f>
+        <v>1E-10</v>
+      </c>
+      <c r="O221" s="83">
         <f t="shared" ref="M221:X221" si="71">0.00000000005 / 10 / 8</f>
-        <v>6.2500000000000006E-13</v>
-      </c>
-      <c r="N221" s="83">
-        <f t="shared" si="71"/>
-        <v>6.2500000000000006E-13</v>
-      </c>
-      <c r="O221" s="83">
-        <f t="shared" si="71"/>
         <v>6.2500000000000006E-13</v>
       </c>
       <c r="P221" s="83">
@@ -23095,16 +23096,14 @@
         <v>4.9999999999999998E-7</v>
       </c>
       <c r="L222" s="83"/>
-      <c r="M222" s="83">
+      <c r="M222" s="101">
+        <v>0</v>
+      </c>
+      <c r="N222" s="101">
+        <v>1</v>
+      </c>
+      <c r="O222" s="83">
         <f t="shared" ref="M222:X222" si="72">0.0000001 / 2</f>
-        <v>4.9999999999999998E-8</v>
-      </c>
-      <c r="N222" s="83">
-        <f t="shared" si="72"/>
-        <v>4.9999999999999998E-8</v>
-      </c>
-      <c r="O222" s="83">
-        <f t="shared" si="72"/>
         <v>4.9999999999999998E-8</v>
       </c>
       <c r="P222" s="83">
@@ -23579,16 +23578,16 @@
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="L227" s="99"/>
-      <c r="M227" s="99">
+      <c r="M227" s="101">
+        <f>0.00001 / 10</f>
+        <v>1.0000000000000002E-6</v>
+      </c>
+      <c r="N227" s="101">
+        <f>0.00001 / 10</f>
+        <v>1.0000000000000002E-6</v>
+      </c>
+      <c r="O227" s="99">
         <f t="shared" ref="M227:X227" si="76">0.00001 / 3</f>
-        <v>3.3333333333333337E-6</v>
-      </c>
-      <c r="N227" s="99">
-        <f t="shared" si="76"/>
-        <v>3.3333333333333337E-6</v>
-      </c>
-      <c r="O227" s="99">
-        <f t="shared" si="76"/>
         <v>3.3333333333333337E-6</v>
       </c>
       <c r="P227" s="99">
@@ -24128,13 +24127,13 @@
         <v>5.0000000000000004E-6</v>
       </c>
       <c r="L233" s="83"/>
-      <c r="M233" s="83">
-        <f>0.00001 /2</f>
-        <v>5.0000000000000004E-6</v>
-      </c>
-      <c r="N233" s="83">
-        <f>0.00001 /2</f>
-        <v>5.0000000000000004E-6</v>
+      <c r="M233" s="101">
+        <f>0.00001 /2 / 10</f>
+        <v>5.0000000000000008E-7</v>
+      </c>
+      <c r="N233" s="101">
+        <f>0.00001 /2 / 10</f>
+        <v>5.0000000000000008E-7</v>
       </c>
       <c r="O233" s="83">
         <f t="shared" ref="O233:V233" si="79">0.00001 /2</f>
@@ -24191,7 +24190,7 @@
       </c>
       <c r="AC233" s="1" t="b">
         <f t="shared" si="66"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234" spans="1:29" x14ac:dyDescent="0.25">
@@ -24230,16 +24229,16 @@
         <v>5.0000000000000004E-6</v>
       </c>
       <c r="L234" s="83"/>
-      <c r="M234" s="83">
+      <c r="M234" s="101">
+        <f>0.000000005 / 5 / 100</f>
+        <v>1.0000000000000001E-11</v>
+      </c>
+      <c r="N234" s="101">
+        <f>0.000000005 / 5 / 100</f>
+        <v>1.0000000000000001E-11</v>
+      </c>
+      <c r="O234" s="83">
         <f t="shared" ref="M234:X234" si="80">0.000000005 / 5</f>
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="N234" s="83">
-        <f t="shared" si="80"/>
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="O234" s="83">
-        <f t="shared" si="80"/>
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="P234" s="83">
@@ -24465,6 +24464,304 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G235:I236">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G236:AA236">
+    <cfRule type="colorScale" priority="363">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="364">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H129:AA130">
+    <cfRule type="colorScale" priority="365">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H212:AA212">
+    <cfRule type="colorScale" priority="367">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="366">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H213:AA213">
+    <cfRule type="colorScale" priority="369">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="368">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H214:AA214">
+    <cfRule type="colorScale" priority="370">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="371">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H215:AA215">
+    <cfRule type="colorScale" priority="373">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="372">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H216:AA216">
+    <cfRule type="colorScale" priority="375">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="374">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H217:AA217">
+    <cfRule type="colorScale" priority="377">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="376">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H220:AA220">
+    <cfRule type="colorScale" priority="379">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="378">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H223:AA223 H221:L222 O221:AA222">
+    <cfRule type="colorScale" priority="393">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="392">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H224:AA224">
+    <cfRule type="colorScale" priority="383">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="382">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H228:AA228">
+    <cfRule type="colorScale" priority="387">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="386">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H229:AA232 H233:L234 O233:AA234">
+    <cfRule type="colorScale" priority="389">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="388">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J235">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -24486,8 +24783,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G236:AA236">
-    <cfRule type="colorScale" priority="361">
+  <conditionalFormatting sqref="K235:L236">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -24497,7 +24794,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="362">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -24508,173 +24805,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H129:AA130">
-    <cfRule type="colorScale" priority="363">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H212:AA212">
-    <cfRule type="colorScale" priority="364">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="365">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H213:AA213">
-    <cfRule type="colorScale" priority="366">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="367">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H214:AA214">
-    <cfRule type="colorScale" priority="368">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="369">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H215:AA215">
-    <cfRule type="colorScale" priority="370">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="371">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H216:AA216">
-    <cfRule type="colorScale" priority="372">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="373">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H217:AA217">
-    <cfRule type="colorScale" priority="374">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="375">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H220:AA220">
-    <cfRule type="colorScale" priority="376">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="377">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H221:AA223">
+  <conditionalFormatting sqref="M235:AA236">
     <cfRule type="colorScale" priority="390">
       <colorScale>
         <cfvo type="min"/>
@@ -24696,29 +24827,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H224:AA224">
-    <cfRule type="colorScale" priority="380">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="381">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H228:AA228">
+  <conditionalFormatting sqref="AA225:AB225 AA226 H225:Z226">
     <cfRule type="colorScale" priority="384">
       <colorScale>
         <cfvo type="min"/>
@@ -24740,118 +24849,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H229:AA234">
-    <cfRule type="colorScale" priority="386">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="387">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J235">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K235:L236">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M235:AA236">
-    <cfRule type="colorScale" priority="388">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="389">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA225:AB225 AA226 H225:Z226">
-    <cfRule type="colorScale" priority="382">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="383">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="AD129:AE130">
-    <cfRule type="colorScale" priority="51">
+    <cfRule type="colorScale" priority="53">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -24863,7 +24862,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD131:AE131 H131:AB131">
-    <cfRule type="colorScale" priority="295">
+    <cfRule type="colorScale" priority="297">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -24873,7 +24872,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="296">
+    <cfRule type="colorScale" priority="298">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -24885,7 +24884,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD132:AE132 H132:AA132">
-    <cfRule type="colorScale" priority="299">
+    <cfRule type="colorScale" priority="301">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -24895,7 +24894,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="300">
+    <cfRule type="colorScale" priority="302">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -24907,7 +24906,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD134:AE134 H134:AB134">
-    <cfRule type="colorScale" priority="303">
+    <cfRule type="colorScale" priority="306">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -24917,7 +24916,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="304">
+    <cfRule type="colorScale" priority="305">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -24929,7 +24928,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD135:AE135 H135:AA135">
-    <cfRule type="colorScale" priority="307">
+    <cfRule type="colorScale" priority="310">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -24939,7 +24938,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="308">
+    <cfRule type="colorScale" priority="309">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -24951,7 +24950,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD140:AE140 H140:AB140">
-    <cfRule type="colorScale" priority="311">
+    <cfRule type="colorScale" priority="313">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -24963,7 +24962,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD146:AE146 H146:AA146">
-    <cfRule type="colorScale" priority="313">
+    <cfRule type="colorScale" priority="315">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -24973,7 +24972,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="314">
+    <cfRule type="colorScale" priority="316">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -24983,7 +24982,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="315">
+    <cfRule type="colorScale" priority="317">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -24995,7 +24994,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD162:AE162 H162:AA162">
-    <cfRule type="colorScale" priority="319">
+    <cfRule type="colorScale" priority="322">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -25005,7 +25004,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="320">
+    <cfRule type="colorScale" priority="323">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -25027,17 +25026,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD168:AE168 H168:AA168">
-    <cfRule type="colorScale" priority="325">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="326">
+    <cfRule type="colorScale" priority="328">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -25048,6 +25037,16 @@
       </colorScale>
     </cfRule>
     <cfRule type="colorScale" priority="327">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="329">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/simulations/scene/inputs/Scenarios_24_11_10.xlsx
+++ b/simulations/scene/inputs/Scenarios_24_11_10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TIGERA~1\AppData\Local\Temp\scp16920\home\torisuten\package\Wheat-BRIDGES\Root_BRIDGES\simulations\scene\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DC8005E-FC92-4DCF-8E4E-8FF6E48B0BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C18BBDE0-1AF8-4D9A-AB75-86E63EC42322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2488,7 +2488,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2696,7 +2696,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="11" fontId="16" fillId="51" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -22904,15 +22903,15 @@
       </c>
       <c r="L220" s="83"/>
       <c r="M220" s="83">
-        <f t="shared" ref="M220:X220" si="70" xml:space="preserve"> 0.0000000000025</f>
-        <v>2.4999999999999998E-12</v>
+        <f xml:space="preserve"> 0.0000000000025*10</f>
+        <v>2.4999999999999998E-11</v>
       </c>
       <c r="N220" s="83">
-        <f t="shared" si="70"/>
-        <v>2.4999999999999998E-12</v>
+        <f xml:space="preserve"> 0.0000000000025*10</f>
+        <v>2.4999999999999998E-11</v>
       </c>
       <c r="O220" s="83">
-        <f t="shared" si="70"/>
+        <f t="shared" ref="N220:X220" si="70" xml:space="preserve"> 0.0000000000025</f>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="P220" s="83">
@@ -22962,7 +22961,7 @@
       </c>
       <c r="AC220" s="1" t="b">
         <f t="shared" si="66"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221" spans="1:31" x14ac:dyDescent="0.25">
@@ -23004,16 +23003,16 @@
         <v>5.0000000000000002E-11</v>
       </c>
       <c r="L221" s="83"/>
-      <c r="M221" s="101">
-        <f>0.00000000005 * 2</f>
+      <c r="M221" s="83">
+        <f>0.00000000005 *2</f>
         <v>1E-10</v>
       </c>
-      <c r="N221" s="101">
-        <f>0.00000000005 * 2</f>
+      <c r="N221" s="83">
+        <f>0.00000000005 *2</f>
         <v>1E-10</v>
       </c>
       <c r="O221" s="83">
-        <f t="shared" ref="M221:X221" si="71">0.00000000005 / 10 / 8</f>
+        <f t="shared" ref="N221:X221" si="71">0.00000000005 / 10 / 8</f>
         <v>6.2500000000000006E-13</v>
       </c>
       <c r="P221" s="83">
@@ -23096,14 +23095,14 @@
         <v>4.9999999999999998E-7</v>
       </c>
       <c r="L222" s="83"/>
-      <c r="M222" s="101">
-        <v>0</v>
-      </c>
-      <c r="N222" s="101">
-        <v>1</v>
+      <c r="M222" s="83">
+        <v>0</v>
+      </c>
+      <c r="N222" s="83">
+        <v>0</v>
       </c>
       <c r="O222" s="83">
-        <f t="shared" ref="M222:X222" si="72">0.0000001 / 2</f>
+        <f t="shared" ref="N222:X222" si="72">0.0000001 / 2</f>
         <v>4.9999999999999998E-8</v>
       </c>
       <c r="P222" s="83">
@@ -23578,16 +23577,16 @@
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="L227" s="99"/>
-      <c r="M227" s="101">
-        <f>0.00001 / 10</f>
-        <v>1.0000000000000002E-6</v>
-      </c>
-      <c r="N227" s="101">
-        <f>0.00001 / 10</f>
-        <v>1.0000000000000002E-6</v>
-      </c>
-      <c r="O227" s="99">
-        <f t="shared" ref="M227:X227" si="76">0.00001 / 3</f>
+      <c r="M227" s="83">
+        <f>0.00001 / 10 / 2 / 4</f>
+        <v>1.2500000000000002E-7</v>
+      </c>
+      <c r="N227" s="83">
+        <f>0.00001 / 10 / 2 / 4</f>
+        <v>1.2500000000000002E-7</v>
+      </c>
+      <c r="O227" s="83">
+        <f t="shared" ref="N227:X227" si="76">0.00001 / 3</f>
         <v>3.3333333333333337E-6</v>
       </c>
       <c r="P227" s="99">
@@ -24127,16 +24126,16 @@
         <v>5.0000000000000004E-6</v>
       </c>
       <c r="L233" s="83"/>
-      <c r="M233" s="101">
-        <f>0.00001 /2 / 10</f>
-        <v>5.0000000000000008E-7</v>
-      </c>
-      <c r="N233" s="101">
-        <f>0.00001 /2 / 10</f>
-        <v>5.0000000000000008E-7</v>
+      <c r="M233" s="83">
+        <f>0.00001 /2</f>
+        <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="N233" s="83">
+        <f t="shared" ref="N233:V233" si="79">0.00001 /2</f>
+        <v>5.0000000000000004E-6</v>
       </c>
       <c r="O233" s="83">
-        <f t="shared" ref="O233:V233" si="79">0.00001 /2</f>
+        <f t="shared" si="79"/>
         <v>5.0000000000000004E-6</v>
       </c>
       <c r="P233" s="83">
@@ -24190,7 +24189,7 @@
       </c>
       <c r="AC233" s="1" t="b">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234" spans="1:29" x14ac:dyDescent="0.25">
@@ -24229,16 +24228,16 @@
         <v>5.0000000000000004E-6</v>
       </c>
       <c r="L234" s="83"/>
-      <c r="M234" s="101">
-        <f>0.000000005 / 5 / 100</f>
-        <v>1.0000000000000001E-11</v>
-      </c>
-      <c r="N234" s="101">
-        <f>0.000000005 / 5 / 100</f>
-        <v>1.0000000000000001E-11</v>
+      <c r="M234" s="83">
+        <f t="shared" ref="M234:X234" si="80">0.000000005 / 5</f>
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="N234" s="83">
+        <f t="shared" si="80"/>
+        <v>1.0000000000000001E-9</v>
       </c>
       <c r="O234" s="83">
-        <f t="shared" ref="M234:X234" si="80">0.000000005 / 5</f>
+        <f t="shared" si="80"/>
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="P234" s="83">
@@ -24464,6 +24463,304 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G235:I236">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G236:AA236">
+    <cfRule type="colorScale" priority="366">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="365">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H129:AA130">
+    <cfRule type="colorScale" priority="367">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H212:AA212">
+    <cfRule type="colorScale" priority="369">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="368">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H213:AA213">
+    <cfRule type="colorScale" priority="371">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="370">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H214:AA214">
+    <cfRule type="colorScale" priority="372">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="373">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H215:AA215">
+    <cfRule type="colorScale" priority="374">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="375">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H216:AA216">
+    <cfRule type="colorScale" priority="377">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="376">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H217:AA217">
+    <cfRule type="colorScale" priority="379">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="378">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H220:AA220">
+    <cfRule type="colorScale" priority="381">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="380">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H221:AA223">
+    <cfRule type="colorScale" priority="394">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="395">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H224:AA224">
+    <cfRule type="colorScale" priority="385">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="384">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H228:AA228">
+    <cfRule type="colorScale" priority="388">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="389">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H229:AA234">
+    <cfRule type="colorScale" priority="391">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="390">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J235">
     <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
@@ -24485,8 +24782,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G236:AA236">
-    <cfRule type="colorScale" priority="363">
+  <conditionalFormatting sqref="K235:L236">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -24496,7 +24793,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="364">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -24507,8 +24804,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H129:AA130">
-    <cfRule type="colorScale" priority="365">
+  <conditionalFormatting sqref="M227:O227">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -24518,283 +24815,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H212:AA212">
-    <cfRule type="colorScale" priority="367">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="366">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H213:AA213">
-    <cfRule type="colorScale" priority="369">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="368">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H214:AA214">
-    <cfRule type="colorScale" priority="370">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="371">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H215:AA215">
-    <cfRule type="colorScale" priority="373">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="372">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H216:AA216">
-    <cfRule type="colorScale" priority="375">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="374">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H217:AA217">
-    <cfRule type="colorScale" priority="377">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="376">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H220:AA220">
-    <cfRule type="colorScale" priority="379">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="378">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H223:AA223 H221:L222 O221:AA222">
-    <cfRule type="colorScale" priority="393">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="392">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H224:AA224">
-    <cfRule type="colorScale" priority="383">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="382">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H228:AA228">
-    <cfRule type="colorScale" priority="387">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="386">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H229:AA232 H233:L234 O233:AA234">
-    <cfRule type="colorScale" priority="389">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="388">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J235">
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K235:L236">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="3">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -24806,7 +24827,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M235:AA236">
-    <cfRule type="colorScale" priority="390">
+    <cfRule type="colorScale" priority="392">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -24816,7 +24837,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="391">
+    <cfRule type="colorScale" priority="393">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -24828,7 +24849,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA225:AB225 AA226 H225:Z226">
-    <cfRule type="colorScale" priority="384">
+    <cfRule type="colorScale" priority="386">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -24838,7 +24859,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="385">
+    <cfRule type="colorScale" priority="387">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -24850,7 +24871,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD129:AE130">
-    <cfRule type="colorScale" priority="53">
+    <cfRule type="colorScale" priority="55">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -24862,7 +24883,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD131:AE131 H131:AB131">
-    <cfRule type="colorScale" priority="297">
+    <cfRule type="colorScale" priority="299">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -24872,7 +24893,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="298">
+    <cfRule type="colorScale" priority="300">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -24884,7 +24905,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD132:AE132 H132:AA132">
-    <cfRule type="colorScale" priority="301">
+    <cfRule type="colorScale" priority="303">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -24894,7 +24915,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="302">
+    <cfRule type="colorScale" priority="304">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -24906,7 +24927,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD134:AE134 H134:AB134">
-    <cfRule type="colorScale" priority="306">
+    <cfRule type="colorScale" priority="308">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -24916,7 +24937,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="305">
+    <cfRule type="colorScale" priority="307">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -24928,7 +24949,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD135:AE135 H135:AA135">
-    <cfRule type="colorScale" priority="310">
+    <cfRule type="colorScale" priority="311">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -24938,7 +24959,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="309">
+    <cfRule type="colorScale" priority="312">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -24950,7 +24971,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD140:AE140 H140:AB140">
-    <cfRule type="colorScale" priority="313">
+    <cfRule type="colorScale" priority="315">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -24962,7 +24983,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD146:AE146 H146:AA146">
-    <cfRule type="colorScale" priority="315">
+    <cfRule type="colorScale" priority="317">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -24972,7 +24993,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="316">
+    <cfRule type="colorScale" priority="318">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -24982,7 +25003,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="317">
+    <cfRule type="colorScale" priority="319">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -24994,7 +25015,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD162:AE162 H162:AA162">
-    <cfRule type="colorScale" priority="322">
+    <cfRule type="colorScale" priority="325">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -25014,7 +25035,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="321">
+    <cfRule type="colorScale" priority="324">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -25026,17 +25047,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD168:AE168 H168:AA168">
-    <cfRule type="colorScale" priority="328">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="327">
+    <cfRule type="colorScale" priority="330">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -25047,6 +25058,16 @@
       </colorScale>
     </cfRule>
     <cfRule type="colorScale" priority="329">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="331">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/simulations/scene/inputs/Scenarios_24_11_10.xlsx
+++ b/simulations/scene/inputs/Scenarios_24_11_10.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TIGERA~1\AppData\Local\Temp\scp36360\home\torisuten\package\Wheat-BRIDGES\Root_BRIDGES\simulations\scene\inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TIGERA~1\AppData\Local\Temp\scp57905\home\torisuten\package\Wheat-BRIDGES\Root_BRIDGES\simulations\scene\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4F1DBBF-2326-45A1-AED6-32826EDEFD64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC9AB57D-F166-475B-A710-D6AA6AAD34D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3220,7 +3220,7 @@
         <v>473</v>
       </c>
       <c r="AD2" s="1" t="b">
-        <f>M2=AB2</f>
+        <f t="shared" ref="AD2:AD65" si="0">M2=AB2</f>
         <v>1</v>
       </c>
       <c r="AE2" s="36" t="s">
@@ -3312,7 +3312,7 @@
         <v>568</v>
       </c>
       <c r="AD3" s="1" t="b">
-        <f>M3=AB3</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE3" s="36" t="s">
@@ -3404,7 +3404,7 @@
         <v>477</v>
       </c>
       <c r="AD4" s="1" t="b">
-        <f>M4=AB4</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE4" s="36" t="s">
@@ -3496,7 +3496,7 @@
         <v>568</v>
       </c>
       <c r="AD5" s="1" t="b">
-        <f>M5=AB5</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE5" s="36" t="s">
@@ -3588,7 +3588,7 @@
         <v>488</v>
       </c>
       <c r="AD6" s="1" t="b">
-        <f>M6=AB6</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE6" s="36" t="s">
@@ -3680,7 +3680,7 @@
         <v>0</v>
       </c>
       <c r="AD7" s="1" t="b">
-        <f>M7=AB7</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE7" s="36">
@@ -3772,7 +3772,7 @@
         <v>87</v>
       </c>
       <c r="AD8" s="1" t="b">
-        <f>M8=AB8</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE8" s="77" t="s">
@@ -3864,7 +3864,7 @@
         <v>1</v>
       </c>
       <c r="AD9" s="1" t="b">
-        <f>M9=AB9</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE9" s="77">
@@ -3956,7 +3956,7 @@
         <v>88</v>
       </c>
       <c r="AD10" s="1" t="b">
-        <f>M10=AB10</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE10" s="77" t="s">
@@ -4048,7 +4048,7 @@
         <v>180</v>
       </c>
       <c r="AD11" s="1" t="b">
-        <f>M11=AB11</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE11" s="85">
@@ -4140,7 +4140,7 @@
         <v>4.1666666999999998E-2</v>
       </c>
       <c r="AD12" s="1" t="b">
-        <f>M12=AB12</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE12" s="78">
@@ -4232,7 +4232,7 @@
         <v>4.1666666999999998E-2</v>
       </c>
       <c r="AD13" s="1" t="b">
-        <f>M13=AB13</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE13" s="79">
@@ -4324,7 +4324,7 @@
         <v>1</v>
       </c>
       <c r="AD14" s="1" t="b">
-        <f>M14=AB14</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE14" s="77">
@@ -4416,7 +4416,7 @@
         <v>0</v>
       </c>
       <c r="AD15" s="1" t="b">
-        <f>M15=AB15</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE15" s="77">
@@ -4508,7 +4508,7 @@
         <v>88</v>
       </c>
       <c r="AD16" s="1" t="b">
-        <f>M16=AB16</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE16" s="77" t="s">
@@ -4600,7 +4600,7 @@
         <v>5.0000000000000001E-9</v>
       </c>
       <c r="AD17" s="1" t="b">
-        <f>M17=AB17</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE17" s="80">
@@ -4692,7 +4692,7 @@
         <v>10</v>
       </c>
       <c r="AD18" s="1" t="b">
-        <f>M18=AB18</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE18" s="77">
@@ -4784,7 +4784,7 @@
         <v>88</v>
       </c>
       <c r="AD19" s="1" t="b">
-        <f>M19=AB19</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE19" s="77" t="s">
@@ -4876,7 +4876,7 @@
         <v>88</v>
       </c>
       <c r="AD20" s="1" t="b">
-        <f>M20=AB20</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE20" s="77" t="s">
@@ -4968,7 +4968,7 @@
         <v>88</v>
       </c>
       <c r="AD21" s="1" t="b">
-        <f>M21=AB21</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE21" s="77" t="s">
@@ -5060,7 +5060,7 @@
         <v>86400</v>
       </c>
       <c r="AD22" s="1" t="b">
-        <f>M22=AB22</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE22" s="77">
@@ -5152,7 +5152,7 @@
         <v>87</v>
       </c>
       <c r="AD23" s="1" t="b">
-        <f>M23=AB23</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE23" s="77" t="s">
@@ -5244,7 +5244,7 @@
         <v>3</v>
       </c>
       <c r="AD24" s="1" t="b">
-        <f>M24=AB24</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE24" s="77">
@@ -5336,7 +5336,7 @@
         <v>88</v>
       </c>
       <c r="AD25" s="1" t="b">
-        <f>M25=AB25</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE25" s="81" t="s">
@@ -5428,7 +5428,7 @@
         <v>88</v>
       </c>
       <c r="AD26" s="1" t="b">
-        <f>M26=AB26</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE26" s="81" t="s">
@@ -5520,7 +5520,7 @@
         <v>88</v>
       </c>
       <c r="AD27" s="1" t="b">
-        <f>M27=AB27</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE27" s="77" t="s">
@@ -5612,7 +5612,7 @@
         <v>88</v>
       </c>
       <c r="AD28" s="1" t="b">
-        <f>M28=AB28</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE28" s="81" t="s">
@@ -5704,7 +5704,7 @@
         <v>88</v>
       </c>
       <c r="AD29" s="1" t="b">
-        <f>M29=AB29</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE29" s="81" t="s">
@@ -5796,7 +5796,7 @@
         <v>88</v>
       </c>
       <c r="AD30" s="1" t="b">
-        <f>M30=AB30</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE30" s="77" t="s">
@@ -5888,7 +5888,7 @@
         <v>0.33</v>
       </c>
       <c r="AD31" s="1" t="b">
-        <f>M31=AB31</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE31" s="77">
@@ -5980,7 +5980,7 @@
         <v>88</v>
       </c>
       <c r="AD32" s="1" t="b">
-        <f>M32=AB32</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE32" s="77" t="s">
@@ -6072,7 +6072,7 @@
         <v>88</v>
       </c>
       <c r="AD33" s="1" t="b">
-        <f>M33=AB33</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE33" s="77" t="s">
@@ -6164,7 +6164,7 @@
         <v>88</v>
       </c>
       <c r="AD34" s="1" t="b">
-        <f>M34=AB34</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE34" s="77" t="s">
@@ -6256,7 +6256,7 @@
         <v>87</v>
       </c>
       <c r="AD35" s="1" t="b">
-        <f>M35=AB35</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE35" s="77" t="s">
@@ -6348,7 +6348,7 @@
         <v>430</v>
       </c>
       <c r="AD36" s="1" t="b">
-        <f>M36=AB36</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE36" s="85" t="s">
@@ -6440,7 +6440,7 @@
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="AD37" s="1" t="b">
-        <f>M37=AB37</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE37" s="80">
@@ -6532,7 +6532,7 @@
         <v>1E-3</v>
       </c>
       <c r="AD38" s="1" t="b">
-        <f>M38=AB38</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE38" s="86">
@@ -6624,7 +6624,7 @@
         <v>87</v>
       </c>
       <c r="AD39" s="1" t="b">
-        <f>M39=AB39</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE39" s="77" t="s">
@@ -6716,7 +6716,7 @@
         <v>89</v>
       </c>
       <c r="AD40" s="1" t="b">
-        <f>M40=AB40</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE40" s="77" t="s">
@@ -6808,7 +6808,7 @@
         <v>87</v>
       </c>
       <c r="AD41" s="1" t="b">
-        <f>M41=AB41</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE41" s="77" t="s">
@@ -6900,7 +6900,7 @@
         <v>88</v>
       </c>
       <c r="AD42" s="1" t="b">
-        <f>M42=AB42</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE42" s="77" t="s">
@@ -6992,7 +6992,7 @@
         <v>120</v>
       </c>
       <c r="AD43" s="1" t="b">
-        <f>M43=AB43</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE43" s="77">
@@ -7084,7 +7084,7 @@
         <v>0</v>
       </c>
       <c r="AD44" s="1" t="b">
-        <f>M44=AB44</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE44" s="77">
@@ -7176,7 +7176,7 @@
         <v>0</v>
       </c>
       <c r="AD45" s="1" t="b">
-        <f>M45=AB45</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE45" s="77">
@@ -7268,7 +7268,7 @@
         <v>-0.1</v>
       </c>
       <c r="AD46" s="1" t="b">
-        <f>M46=AB46</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE46" s="77">
@@ -7360,7 +7360,7 @@
         <v>-0.2</v>
       </c>
       <c r="AD47" s="1" t="b">
-        <f>M47=AB47</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE47" s="77">
@@ -7452,7 +7452,7 @@
         <v>0.4</v>
       </c>
       <c r="AD48" s="1" t="b">
-        <f>M48=AB48</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE48" s="77">
@@ -7544,7 +7544,7 @@
         <v>0</v>
       </c>
       <c r="AD49" s="1" t="b">
-        <f>M49=AB49</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE49" s="77">
@@ -7636,7 +7636,7 @@
         <v>1200</v>
       </c>
       <c r="AD50" s="1" t="b">
-        <f>M50=AB50</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE50" s="77">
@@ -7728,7 +7728,7 @@
         <v>1200</v>
       </c>
       <c r="AD51" s="1" t="b">
-        <f>M51=AB51</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE51" s="77">
@@ -7820,7 +7820,7 @@
         <v>457</v>
       </c>
       <c r="AD52" s="1" t="b">
-        <f>M52=AB52</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE52" s="35" t="s">
@@ -7912,7 +7912,7 @@
         <v>87</v>
       </c>
       <c r="AD53" s="1" t="b">
-        <f>M53=AB53</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE53" s="77" t="s">
@@ -8004,7 +8004,7 @@
         <v>87</v>
       </c>
       <c r="AD54" s="1" t="b">
-        <f>M54=AB54</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE54" s="77" t="s">
@@ -8096,7 +8096,7 @@
         <v>0</v>
       </c>
       <c r="AD55" s="1" t="b">
-        <f>M55=AB55</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE55" s="77">
@@ -8188,7 +8188,7 @@
         <v>0.5</v>
       </c>
       <c r="AD56" s="1" t="b">
-        <f>M56=AB56</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE56" s="77">
@@ -8280,7 +8280,7 @@
         <v>0.05</v>
       </c>
       <c r="AD57" s="1" t="b">
-        <f>M57=AB57</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE57" s="77">
@@ -8372,7 +8372,7 @@
         <v>1E-3</v>
       </c>
       <c r="AD58" s="1" t="b">
-        <f>M58=AB58</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE58" s="80">
@@ -8464,7 +8464,7 @@
         <v>0</v>
       </c>
       <c r="AD59" s="1" t="b">
-        <f>M59=AB59</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE59" s="77">
@@ -8556,7 +8556,7 @@
         <v>1E-4</v>
       </c>
       <c r="AD60" s="1" t="b">
-        <f>M60=AB60</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE60" s="77">
@@ -8648,7 +8648,7 @@
         <v>1E-4</v>
       </c>
       <c r="AD61" s="1" t="b">
-        <f>M61=AB61</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE61" s="77">
@@ -8740,7 +8740,7 @@
         <v>6.9999999999999999E-4</v>
       </c>
       <c r="AD62" s="1" t="b">
-        <f>M62=AB62</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE62" s="77">
@@ -8832,7 +8832,7 @@
         <v>1.22E-4</v>
       </c>
       <c r="AD63" s="1" t="b">
-        <f>M63=AB63</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE63" s="77">
@@ -8924,7 +8924,7 @@
         <v>1</v>
       </c>
       <c r="AD64" s="1" t="b">
-        <f>M64=AB64</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE64" s="77">
@@ -9016,7 +9016,7 @@
         <v>0.95</v>
       </c>
       <c r="AD65" s="1" t="b">
-        <f>M65=AB65</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AE65" s="77">
@@ -9108,7 +9108,7 @@
         <v>88</v>
       </c>
       <c r="AD66" s="1" t="b">
-        <f>M66=AB66</f>
+        <f t="shared" ref="AD66:AD129" si="1">M66=AB66</f>
         <v>1</v>
       </c>
       <c r="AE66" s="77" t="s">
@@ -9200,7 +9200,7 @@
         <v>5</v>
       </c>
       <c r="AD67" s="1" t="b">
-        <f>M67=AB67</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE67" s="77">
@@ -9292,7 +9292,7 @@
         <v>88</v>
       </c>
       <c r="AD68" s="1" t="b">
-        <f>M68=AB68</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE68" s="77" t="s">
@@ -9384,7 +9384,7 @@
         <v>50</v>
       </c>
       <c r="AD69" s="1" t="b">
-        <f>M69=AB69</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE69" s="77">
@@ -9476,7 +9476,7 @@
         <v>1453890.8941884842</v>
       </c>
       <c r="AD70" s="1" t="b">
-        <f>M70=AB70</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE70" s="78">
@@ -9568,7 +9568,7 @@
         <v>1.3888888888888888E-5</v>
       </c>
       <c r="AD71" s="1" t="b">
-        <f>M71=AB71</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE71" s="78">
@@ -9660,7 +9660,7 @@
         <v>6.5011574074074071E-4</v>
       </c>
       <c r="AD72" s="1" t="b">
-        <f>M72=AB72</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE72" s="79">
@@ -9752,7 +9752,7 @@
         <v>4.7400000000000003E-3</v>
       </c>
       <c r="AD73" s="1" t="b">
-        <f>M73=AB73</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE73" s="85">
@@ -9798,52 +9798,52 @@
       </c>
       <c r="L74" s="79"/>
       <c r="M74" s="79">
-        <f t="shared" ref="M74:Y74" si="0">282528</f>
+        <f t="shared" ref="M74:Y74" si="2">282528</f>
         <v>282528</v>
       </c>
       <c r="N74" s="79">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>282528</v>
       </c>
       <c r="O74" s="79">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>282528</v>
       </c>
       <c r="P74" s="79">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>282528</v>
       </c>
       <c r="Q74" s="79">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>282528</v>
       </c>
       <c r="R74" s="79">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>282528</v>
       </c>
       <c r="S74" s="79">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>282528</v>
       </c>
       <c r="T74" s="79">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>282528</v>
       </c>
       <c r="U74" s="79">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>282528</v>
       </c>
       <c r="V74" s="79">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>282528</v>
       </c>
       <c r="W74" s="79">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>282528</v>
       </c>
       <c r="X74" s="79"/>
       <c r="Y74" s="79">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>282528</v>
       </c>
       <c r="Z74" s="79">
@@ -9858,7 +9858,7 @@
         <v>282528</v>
       </c>
       <c r="AD74" s="1" t="b">
-        <f>M74=AB74</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE74" s="79">
@@ -9950,7 +9950,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="AD75" s="1" t="b">
-        <f>M75=AB75</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE75" s="85">
@@ -10042,7 +10042,7 @@
         <v>0.16</v>
       </c>
       <c r="AD76" s="1" t="b">
-        <f>M76=AB76</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE76" s="87">
@@ -10134,7 +10134,7 @@
         <v>0</v>
       </c>
       <c r="AD77" s="1" t="b">
-        <f>M77=AB77</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE77" s="77">
@@ -10226,7 +10226,7 @@
         <v>745476480000</v>
       </c>
       <c r="AD78" s="1" t="b">
-        <f>M78=AB78</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE78" s="78">
@@ -10318,7 +10318,7 @@
         <v>100</v>
       </c>
       <c r="AD79" s="1" t="b">
-        <f>M79=AB79</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE79" s="77">
@@ -10410,7 +10410,7 @@
         <v>87</v>
       </c>
       <c r="AD80" s="1" t="b">
-        <f>M80=AB80</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE80" s="77" t="s">
@@ -10502,7 +10502,7 @@
         <v>21600</v>
       </c>
       <c r="AD81" s="1" t="b">
-        <f>M81=AB81</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE81" s="85">
@@ -10594,7 +10594,7 @@
         <v>0.5</v>
       </c>
       <c r="AD82" s="1" t="b">
-        <f>M82=AB82</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE82" s="77">
@@ -10686,7 +10686,7 @@
         <v>60479.999999999993</v>
       </c>
       <c r="AD83" s="1" t="b">
-        <f>M83=AB83</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE83" s="85">
@@ -10778,7 +10778,7 @@
         <v>0.85</v>
       </c>
       <c r="AD84" s="1" t="b">
-        <f>M84=AB84</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE84" s="77">
@@ -10870,7 +10870,7 @@
         <v>518400</v>
       </c>
       <c r="AD85" s="1" t="b">
-        <f>M85=AB85</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE85" s="77">
@@ -10962,7 +10962,7 @@
         <v>5184000</v>
       </c>
       <c r="AD86" s="1" t="b">
-        <f>M86=AB86</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE86" s="77">
@@ -11054,7 +11054,7 @@
         <v>50000</v>
       </c>
       <c r="AD87" s="1" t="b">
-        <f>M87=AB87</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE87" s="86">
@@ -11146,7 +11146,7 @@
         <v>140000</v>
       </c>
       <c r="AD88" s="1" t="b">
-        <f>M88=AB88</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE88" s="77">
@@ -11238,7 +11238,7 @@
         <v>3.6636136999999999E-2</v>
       </c>
       <c r="AD89" s="1" t="b">
-        <f>M89=AB89</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE89" s="78">
@@ -11330,7 +11330,7 @@
         <v>4.4999999999999997E-3</v>
       </c>
       <c r="AD90" s="1" t="b">
-        <f>M90=AB90</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE90" s="77">
@@ -11422,7 +11422,7 @@
         <v>0.05</v>
       </c>
       <c r="AD91" s="1" t="b">
-        <f>M91=AB91</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE91" s="77">
@@ -11514,7 +11514,7 @@
         <v>6.0000000000000002E-6</v>
       </c>
       <c r="AD92" s="1" t="b">
-        <f>M92=AB92</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE92" s="77">
@@ -11606,7 +11606,7 @@
         <v>1E-3</v>
       </c>
       <c r="AD93" s="1" t="b">
-        <f>M93=AB93</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE93" s="77">
@@ -11698,7 +11698,7 @@
         <v>374999999.99999994</v>
       </c>
       <c r="AD94" s="1" t="b">
-        <f>M94=AB94</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE94" s="77">
@@ -11790,7 +11790,7 @@
         <v>3.7037037037037038E-3</v>
       </c>
       <c r="AD95" s="1" t="b">
-        <f>M95=AB95</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE95" s="78">
@@ -11882,7 +11882,7 @@
         <v>165600</v>
       </c>
       <c r="AD96" s="1" t="b">
-        <f>M96=AB96</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE96" s="77">
@@ -11974,7 +11974,7 @@
         <v>20</v>
       </c>
       <c r="AD97" s="1" t="b">
-        <f>M97=AB97</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE97" s="77">
@@ -12066,7 +12066,7 @@
         <v>1</v>
       </c>
       <c r="AD98" s="1" t="b">
-        <f>M98=AB98</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE98" s="77">
@@ -12158,7 +12158,7 @@
         <v>21</v>
       </c>
       <c r="AD99" s="1" t="b">
-        <f>M99=AB99</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE99" s="77">
@@ -12250,7 +12250,7 @@
         <v>0.64</v>
       </c>
       <c r="AD100" s="1" t="b">
-        <f>M100=AB100</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE100" s="77">
@@ -12342,7 +12342,7 @@
         <v>8</v>
       </c>
       <c r="AD101" s="1" t="b">
-        <f>M101=AB101</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE101" s="77">
@@ -12434,7 +12434,7 @@
         <v>10</v>
       </c>
       <c r="AD102" s="1" t="b">
-        <f>M102=AB102</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE102" s="77">
@@ -12526,7 +12526,7 @@
         <v>8</v>
       </c>
       <c r="AD103" s="1" t="b">
-        <f>M103=AB103</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE103" s="77">
@@ -12618,7 +12618,7 @@
         <v>1</v>
       </c>
       <c r="AD104" s="1" t="b">
-        <f>M104=AB104</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE104" s="77">
@@ -12710,7 +12710,7 @@
         <v>0.5</v>
       </c>
       <c r="AD105" s="1" t="b">
-        <f>M105=AB105</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE105" s="77">
@@ -12740,89 +12740,89 @@
         <v>497</v>
       </c>
       <c r="G106" s="58">
-        <f t="shared" ref="G106:Q106" si="1">G104</f>
+        <f t="shared" ref="G106:Q106" si="3">G104</f>
         <v>1</v>
       </c>
       <c r="H106" s="58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="I106" s="58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J106" s="58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K106" s="58">
-        <f t="shared" ref="K106" si="2">K104</f>
+        <f t="shared" ref="K106" si="4">K104</f>
         <v>1</v>
       </c>
       <c r="L106" s="58"/>
       <c r="M106" s="58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N106" s="58">
-        <f t="shared" ref="N106" si="3">N104</f>
+        <f t="shared" ref="N106" si="5">N104</f>
         <v>1</v>
       </c>
       <c r="O106" s="58">
-        <f t="shared" ref="O106" si="4">O104</f>
+        <f t="shared" ref="O106" si="6">O104</f>
         <v>1</v>
       </c>
       <c r="P106" s="58">
-        <f t="shared" ref="P106" si="5">P104</f>
+        <f t="shared" ref="P106" si="7">P104</f>
         <v>1</v>
       </c>
       <c r="Q106" s="58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="R106" s="58">
-        <f t="shared" ref="R106" si="6">R104</f>
+        <f t="shared" ref="R106" si="8">R104</f>
         <v>1</v>
       </c>
       <c r="S106" s="58">
-        <f t="shared" ref="S106:W106" si="7">S104</f>
+        <f t="shared" ref="S106:W106" si="9">S104</f>
         <v>1</v>
       </c>
       <c r="T106" s="58">
-        <f t="shared" ref="T106:U106" si="8">T104</f>
+        <f t="shared" ref="T106:U106" si="10">T104</f>
         <v>1</v>
       </c>
       <c r="U106" s="58">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="V106" s="58">
-        <f t="shared" ref="V106" si="9">V104</f>
+        <f t="shared" ref="V106" si="11">V104</f>
         <v>1</v>
       </c>
       <c r="W106" s="58">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="X106" s="58"/>
       <c r="Y106" s="58">
-        <f t="shared" ref="Y106" si="10">Y104</f>
+        <f t="shared" ref="Y106" si="12">Y104</f>
         <v>1</v>
       </c>
       <c r="Z106" s="58">
-        <f t="shared" ref="Z106" si="11">Z104</f>
+        <f t="shared" ref="Z106" si="13">Z104</f>
         <v>1</v>
       </c>
       <c r="AA106" s="58">
-        <f t="shared" ref="AA106" si="12">AA104</f>
+        <f t="shared" ref="AA106" si="14">AA104</f>
         <v>1</v>
       </c>
       <c r="AB106" s="58">
-        <f t="shared" ref="AB106" si="13">AB104</f>
+        <f t="shared" ref="AB106" si="15">AB104</f>
         <v>1</v>
       </c>
       <c r="AD106" s="1" t="b">
-        <f>M106=AB106</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE106" s="58">
@@ -12856,85 +12856,85 @@
         <v>3</v>
       </c>
       <c r="H107" s="58">
-        <f t="shared" ref="H107:AB107" si="14">150*H104</f>
+        <f t="shared" ref="H107:AB107" si="16">150*H104</f>
         <v>150</v>
       </c>
       <c r="I107" s="58">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>150</v>
       </c>
       <c r="J107" s="58">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>150</v>
       </c>
       <c r="K107" s="58">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>150</v>
       </c>
       <c r="L107" s="58"/>
       <c r="M107" s="58">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>150</v>
       </c>
       <c r="N107" s="58">
-        <f t="shared" ref="N107" si="15">150*N104</f>
+        <f t="shared" ref="N107" si="17">150*N104</f>
         <v>150</v>
       </c>
       <c r="O107" s="58">
-        <f t="shared" ref="O107" si="16">150*O104</f>
+        <f t="shared" ref="O107" si="18">150*O104</f>
         <v>150</v>
       </c>
       <c r="P107" s="58">
-        <f t="shared" ref="P107" si="17">150*P104</f>
+        <f t="shared" ref="P107" si="19">150*P104</f>
         <v>150</v>
       </c>
       <c r="Q107" s="58">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>150</v>
       </c>
       <c r="R107" s="58">
-        <f t="shared" ref="R107" si="18">150*R104</f>
+        <f t="shared" ref="R107" si="20">150*R104</f>
         <v>150</v>
       </c>
       <c r="S107" s="58">
-        <f t="shared" ref="S107:W107" si="19">150*S104</f>
+        <f t="shared" ref="S107:W107" si="21">150*S104</f>
         <v>150</v>
       </c>
       <c r="T107" s="58">
-        <f t="shared" ref="T107:U107" si="20">150*T104</f>
+        <f t="shared" ref="T107:U107" si="22">150*T104</f>
         <v>150</v>
       </c>
       <c r="U107" s="58">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>150</v>
       </c>
       <c r="V107" s="58">
-        <f t="shared" ref="V107" si="21">150*V104</f>
+        <f t="shared" ref="V107" si="23">150*V104</f>
         <v>150</v>
       </c>
       <c r="W107" s="58">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>150</v>
       </c>
       <c r="X107" s="58"/>
       <c r="Y107" s="58">
-        <f t="shared" ref="Y107" si="22">150*Y104</f>
+        <f t="shared" ref="Y107" si="24">150*Y104</f>
         <v>150</v>
       </c>
       <c r="Z107" s="58">
-        <f t="shared" ref="Z107" si="23">150*Z104</f>
+        <f t="shared" ref="Z107" si="25">150*Z104</f>
         <v>150</v>
       </c>
       <c r="AA107" s="58">
-        <f t="shared" ref="AA107" si="24">150*AA104</f>
+        <f t="shared" ref="AA107" si="26">150*AA104</f>
         <v>150</v>
       </c>
       <c r="AB107" s="58">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>150</v>
       </c>
       <c r="AD107" s="1" t="b">
-        <f>M107=AB107</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE107" s="58">
@@ -12964,89 +12964,89 @@
         <v>497</v>
       </c>
       <c r="G108" s="58">
-        <f t="shared" ref="G108:Q108" si="25">G99</f>
+        <f t="shared" ref="G108:Q108" si="27">G99</f>
         <v>21</v>
       </c>
       <c r="H108" s="58">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>21</v>
       </c>
       <c r="I108" s="58">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>21</v>
       </c>
       <c r="J108" s="58">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>21</v>
       </c>
       <c r="K108" s="58">
-        <f t="shared" ref="K108" si="26">K99</f>
+        <f t="shared" ref="K108" si="28">K99</f>
         <v>21</v>
       </c>
       <c r="L108" s="58"/>
       <c r="M108" s="58">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>21</v>
       </c>
       <c r="N108" s="58">
-        <f t="shared" ref="N108" si="27">N99</f>
+        <f t="shared" ref="N108" si="29">N99</f>
         <v>21</v>
       </c>
       <c r="O108" s="58">
-        <f t="shared" ref="O108" si="28">O99</f>
+        <f t="shared" ref="O108" si="30">O99</f>
         <v>21</v>
       </c>
       <c r="P108" s="58">
-        <f t="shared" ref="P108" si="29">P99</f>
+        <f t="shared" ref="P108" si="31">P99</f>
         <v>21</v>
       </c>
       <c r="Q108" s="58">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>21</v>
       </c>
       <c r="R108" s="58">
-        <f t="shared" ref="R108" si="30">R99</f>
+        <f t="shared" ref="R108" si="32">R99</f>
         <v>21</v>
       </c>
       <c r="S108" s="58">
-        <f t="shared" ref="S108:W108" si="31">S99</f>
+        <f t="shared" ref="S108:W108" si="33">S99</f>
         <v>21</v>
       </c>
       <c r="T108" s="58">
-        <f t="shared" ref="T108:U108" si="32">T99</f>
+        <f t="shared" ref="T108:U108" si="34">T99</f>
         <v>21</v>
       </c>
       <c r="U108" s="58">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>21</v>
       </c>
       <c r="V108" s="58">
-        <f t="shared" ref="V108" si="33">V99</f>
+        <f t="shared" ref="V108" si="35">V99</f>
         <v>21</v>
       </c>
       <c r="W108" s="58">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>21</v>
       </c>
       <c r="X108" s="58"/>
       <c r="Y108" s="58">
-        <f t="shared" ref="Y108" si="34">Y99</f>
+        <f t="shared" ref="Y108" si="36">Y99</f>
         <v>21</v>
       </c>
       <c r="Z108" s="58">
-        <f t="shared" ref="Z108" si="35">Z99</f>
+        <f t="shared" ref="Z108" si="37">Z99</f>
         <v>21</v>
       </c>
       <c r="AA108" s="58">
-        <f t="shared" ref="AA108" si="36">AA99</f>
+        <f t="shared" ref="AA108" si="38">AA99</f>
         <v>21</v>
       </c>
       <c r="AB108" s="58">
-        <f t="shared" ref="AB108" si="37">AB99</f>
+        <f t="shared" ref="AB108" si="39">AB99</f>
         <v>21</v>
       </c>
       <c r="AD108" s="1" t="b">
-        <f>M108=AB108</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE108" s="58">
@@ -13080,85 +13080,85 @@
         <v>210</v>
       </c>
       <c r="H109" s="58">
-        <f t="shared" ref="H109:AB109" si="38">70*H99</f>
+        <f t="shared" ref="H109:AB109" si="40">70*H99</f>
         <v>1470</v>
       </c>
       <c r="I109" s="58">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>1470</v>
       </c>
       <c r="J109" s="58">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>1470</v>
       </c>
       <c r="K109" s="58">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>1470</v>
       </c>
       <c r="L109" s="58"/>
       <c r="M109" s="58">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>1470</v>
       </c>
       <c r="N109" s="58">
-        <f t="shared" ref="N109" si="39">70*N99</f>
+        <f t="shared" ref="N109" si="41">70*N99</f>
         <v>1470</v>
       </c>
       <c r="O109" s="58">
-        <f t="shared" ref="O109" si="40">70*O99</f>
+        <f t="shared" ref="O109" si="42">70*O99</f>
         <v>1470</v>
       </c>
       <c r="P109" s="58">
-        <f t="shared" ref="P109" si="41">70*P99</f>
+        <f t="shared" ref="P109" si="43">70*P99</f>
         <v>1470</v>
       </c>
       <c r="Q109" s="58">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>1470</v>
       </c>
       <c r="R109" s="58">
-        <f t="shared" ref="R109" si="42">70*R99</f>
+        <f t="shared" ref="R109" si="44">70*R99</f>
         <v>1470</v>
       </c>
       <c r="S109" s="58">
-        <f t="shared" ref="S109:W109" si="43">70*S99</f>
+        <f t="shared" ref="S109:W109" si="45">70*S99</f>
         <v>1470</v>
       </c>
       <c r="T109" s="58">
-        <f t="shared" ref="T109:U109" si="44">70*T99</f>
+        <f t="shared" ref="T109:U109" si="46">70*T99</f>
         <v>1470</v>
       </c>
       <c r="U109" s="58">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>1470</v>
       </c>
       <c r="V109" s="58">
-        <f t="shared" ref="V109" si="45">70*V99</f>
+        <f t="shared" ref="V109" si="47">70*V99</f>
         <v>1470</v>
       </c>
       <c r="W109" s="58">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>1470</v>
       </c>
       <c r="X109" s="58"/>
       <c r="Y109" s="58">
-        <f t="shared" ref="Y109" si="46">70*Y99</f>
+        <f t="shared" ref="Y109" si="48">70*Y99</f>
         <v>1470</v>
       </c>
       <c r="Z109" s="58">
-        <f t="shared" ref="Z109" si="47">70*Z99</f>
+        <f t="shared" ref="Z109" si="49">70*Z99</f>
         <v>1470</v>
       </c>
       <c r="AA109" s="58">
-        <f t="shared" ref="AA109" si="48">70*AA99</f>
+        <f t="shared" ref="AA109" si="50">70*AA99</f>
         <v>1470</v>
       </c>
       <c r="AB109" s="58">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>1470</v>
       </c>
       <c r="AD109" s="1" t="b">
-        <f>M109=AB109</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE109" s="58">
@@ -13250,7 +13250,7 @@
         <v>0</v>
       </c>
       <c r="AD110" s="1" t="b">
-        <f>M110=AB110</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE110" s="77">
@@ -13342,7 +13342,7 @@
         <v>1589759.9999999998</v>
       </c>
       <c r="AD111" s="1" t="b">
-        <f>M111=AB111</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE111" s="82">
@@ -13434,7 +13434,7 @@
         <v>6171428.5714285718</v>
       </c>
       <c r="AD112" s="1" t="b">
-        <f>M112=AB112</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE112" s="82">
@@ -13526,7 +13526,7 @@
         <v>6171428.5714285718</v>
       </c>
       <c r="AD113" s="1" t="b">
-        <f>M113=AB113</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE113" s="82">
@@ -13618,7 +13618,7 @@
         <v>100</v>
       </c>
       <c r="AD114" s="1" t="b">
-        <f>M114=AB114</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE114" s="82">
@@ -13652,19 +13652,19 @@
         <v>280800</v>
       </c>
       <c r="H115" s="67">
-        <f t="shared" ref="H115:AB115" si="49">0.1 * 3.25 * (60*60*24)</f>
+        <f t="shared" ref="H115:AB115" si="51">0.1 * 3.25 * (60*60*24)</f>
         <v>28080</v>
       </c>
       <c r="I115" s="67">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>28080</v>
       </c>
       <c r="J115" s="67">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>28080</v>
       </c>
       <c r="K115" s="67">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>28080</v>
       </c>
       <c r="L115" s="67"/>
@@ -13685,31 +13685,31 @@
         <v>86400</v>
       </c>
       <c r="Q115" s="67">
-        <f t="shared" ref="Q115:W115" si="50">1 * (60*60*24)</f>
+        <f t="shared" ref="Q115:W115" si="52">1 * (60*60*24)</f>
         <v>86400</v>
       </c>
       <c r="R115" s="67">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>86400</v>
       </c>
       <c r="S115" s="67">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>86400</v>
       </c>
       <c r="T115" s="67">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>86400</v>
       </c>
       <c r="U115" s="67">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>86400</v>
       </c>
       <c r="V115" s="67">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>86400</v>
       </c>
       <c r="W115" s="67">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>86400</v>
       </c>
       <c r="X115" s="67"/>
@@ -13718,19 +13718,19 @@
         <v>86400</v>
       </c>
       <c r="Z115" s="67">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>28080</v>
       </c>
       <c r="AA115" s="67">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>28080</v>
       </c>
       <c r="AB115" s="67">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>28080</v>
       </c>
       <c r="AD115" s="1" t="b">
-        <f>M115=AB115</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE115" s="67">
@@ -13764,19 +13764,19 @@
         <v>1.2847222222222224E-5</v>
       </c>
       <c r="H116" s="67">
-        <f t="shared" ref="H116:AB116" si="51">1.11 / 10</f>
+        <f t="shared" ref="H116:AB116" si="53">1.11 / 10</f>
         <v>0.11100000000000002</v>
       </c>
       <c r="I116" s="67">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0.11100000000000002</v>
       </c>
       <c r="J116" s="67">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0.11100000000000002</v>
       </c>
       <c r="K116" s="67">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0.11100000000000002</v>
       </c>
       <c r="L116" s="67"/>
@@ -13797,31 +13797,31 @@
         <v>1.2152777777777779E-5</v>
       </c>
       <c r="Q116" s="67">
-        <f t="shared" ref="Q116:W116" si="52">1.05 / (60*60*24)</f>
+        <f t="shared" ref="Q116:W116" si="54">1.05 / (60*60*24)</f>
         <v>1.2152777777777779E-5</v>
       </c>
       <c r="R116" s="67">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>1.2152777777777779E-5</v>
       </c>
       <c r="S116" s="67">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>1.2152777777777779E-5</v>
       </c>
       <c r="T116" s="67">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>1.2152777777777779E-5</v>
       </c>
       <c r="U116" s="67">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>1.2152777777777779E-5</v>
       </c>
       <c r="V116" s="67">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>1.2152777777777779E-5</v>
       </c>
       <c r="W116" s="67">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>1.2152777777777779E-5</v>
       </c>
       <c r="X116" s="67"/>
@@ -13830,19 +13830,19 @@
         <v>1.2152777777777779E-5</v>
       </c>
       <c r="Z116" s="67">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0.11100000000000002</v>
       </c>
       <c r="AA116" s="67">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0.11100000000000002</v>
       </c>
       <c r="AB116" s="67">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0.11100000000000002</v>
       </c>
       <c r="AD116" s="1" t="b">
-        <f>M116=AB116</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE116" s="67">
@@ -13934,7 +13934,7 @@
         <v>100</v>
       </c>
       <c r="AD117" s="1" t="b">
-        <f>M117=AB117</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE117" s="82">
@@ -13964,23 +13964,23 @@
         <v>428</v>
       </c>
       <c r="G118" s="67">
-        <f t="shared" ref="G118:AB118" si="53">5.32 * (60*60*24)</f>
+        <f t="shared" ref="G118:AB118" si="55">5.32 * (60*60*24)</f>
         <v>459648</v>
       </c>
       <c r="H118" s="67">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>459648</v>
       </c>
       <c r="I118" s="67">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>459648</v>
       </c>
       <c r="J118" s="67">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>459648</v>
       </c>
       <c r="K118" s="67">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>459648</v>
       </c>
       <c r="L118" s="67"/>
@@ -14001,31 +14001,31 @@
         <v>43200</v>
       </c>
       <c r="Q118" s="67">
-        <f t="shared" ref="Q118:W118" si="54">0.5 * (60*60*24)</f>
+        <f t="shared" ref="Q118:W118" si="56">0.5 * (60*60*24)</f>
         <v>43200</v>
       </c>
       <c r="R118" s="67">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>43200</v>
       </c>
       <c r="S118" s="67">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>43200</v>
       </c>
       <c r="T118" s="67">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>43200</v>
       </c>
       <c r="U118" s="67">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>43200</v>
       </c>
       <c r="V118" s="67">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>43200</v>
       </c>
       <c r="W118" s="67">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>43200</v>
       </c>
       <c r="X118" s="67"/>
@@ -14034,19 +14034,19 @@
         <v>43200</v>
       </c>
       <c r="Z118" s="67">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>459648</v>
       </c>
       <c r="AA118" s="67">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>459648</v>
       </c>
       <c r="AB118" s="67">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>459648</v>
       </c>
       <c r="AD118" s="1" t="b">
-        <f>M118=AB118</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE118" s="67">
@@ -14080,19 +14080,19 @@
         <v>1.2847222222222224E-5</v>
       </c>
       <c r="H119" s="67">
-        <f t="shared" ref="H119:AB119" si="55">1.11/8</f>
+        <f t="shared" ref="H119:AB119" si="57">1.11/8</f>
         <v>0.13875000000000001</v>
       </c>
       <c r="I119" s="67">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>0.13875000000000001</v>
       </c>
       <c r="J119" s="67">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>0.13875000000000001</v>
       </c>
       <c r="K119" s="67">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>0.13875000000000001</v>
       </c>
       <c r="L119" s="67"/>
@@ -14113,31 +14113,31 @@
         <v>8.101851851851852E-6</v>
       </c>
       <c r="Q119" s="67">
-        <f t="shared" ref="Q119:W119" si="56">0.7 / (60*60*24)</f>
+        <f t="shared" ref="Q119:W119" si="58">0.7 / (60*60*24)</f>
         <v>8.101851851851852E-6</v>
       </c>
       <c r="R119" s="67">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>8.101851851851852E-6</v>
       </c>
       <c r="S119" s="67">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>8.101851851851852E-6</v>
       </c>
       <c r="T119" s="67">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>8.101851851851852E-6</v>
       </c>
       <c r="U119" s="67">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>8.101851851851852E-6</v>
       </c>
       <c r="V119" s="67">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>8.101851851851852E-6</v>
       </c>
       <c r="W119" s="67">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>8.101851851851852E-6</v>
       </c>
       <c r="X119" s="67"/>
@@ -14146,19 +14146,19 @@
         <v>8.101851851851852E-6</v>
       </c>
       <c r="Z119" s="67">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>0.13875000000000001</v>
       </c>
       <c r="AA119" s="67">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>0.13875000000000001</v>
       </c>
       <c r="AB119" s="67">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>0.13875000000000001</v>
       </c>
       <c r="AD119" s="1" t="b">
-        <f>M119=AB119</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE119" s="67">
@@ -14250,7 +14250,7 @@
         <v>100</v>
       </c>
       <c r="AD120" s="1" t="b">
-        <f>M120=AB120</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE120" s="82">
@@ -14280,23 +14280,23 @@
         <v>428</v>
       </c>
       <c r="G121" s="67">
-        <f t="shared" ref="G121:AB121" si="57">5.32 * (60*60*24)</f>
+        <f t="shared" ref="G121:AB121" si="59">5.32 * (60*60*24)</f>
         <v>459648</v>
       </c>
       <c r="H121" s="67">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>459648</v>
       </c>
       <c r="I121" s="67">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>459648</v>
       </c>
       <c r="J121" s="67">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>459648</v>
       </c>
       <c r="K121" s="67">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>459648</v>
       </c>
       <c r="L121" s="67"/>
@@ -14317,31 +14317,31 @@
         <v>86400</v>
       </c>
       <c r="Q121" s="67">
-        <f t="shared" ref="Q121:W121" si="58">1 * (60*60*24)</f>
+        <f t="shared" ref="Q121:W121" si="60">1 * (60*60*24)</f>
         <v>86400</v>
       </c>
       <c r="R121" s="67">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>86400</v>
       </c>
       <c r="S121" s="67">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>86400</v>
       </c>
       <c r="T121" s="67">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>86400</v>
       </c>
       <c r="U121" s="67">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>86400</v>
       </c>
       <c r="V121" s="67">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>86400</v>
       </c>
       <c r="W121" s="67">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>86400</v>
       </c>
       <c r="X121" s="67"/>
@@ -14350,19 +14350,19 @@
         <v>86400</v>
       </c>
       <c r="Z121" s="67">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>459648</v>
       </c>
       <c r="AA121" s="67">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>459648</v>
       </c>
       <c r="AB121" s="67">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>459648</v>
       </c>
       <c r="AD121" s="1" t="b">
-        <f>M121=AB121</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE121" s="67">
@@ -14396,19 +14396,19 @@
         <v>1.2847222222222224E-5</v>
       </c>
       <c r="H122" s="67">
-        <f t="shared" ref="H122:AB122" si="59">1.11/8</f>
+        <f t="shared" ref="H122:AB122" si="61">1.11/8</f>
         <v>0.13875000000000001</v>
       </c>
       <c r="I122" s="67">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0.13875000000000001</v>
       </c>
       <c r="J122" s="67">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0.13875000000000001</v>
       </c>
       <c r="K122" s="67">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0.13875000000000001</v>
       </c>
       <c r="L122" s="67"/>
@@ -14429,31 +14429,31 @@
         <v>1.2847222222222224E-5</v>
       </c>
       <c r="Q122" s="67">
-        <f t="shared" ref="Q122:W122" si="60">1.11 / (60*60*24)</f>
+        <f t="shared" ref="Q122:W122" si="62">1.11 / (60*60*24)</f>
         <v>1.2847222222222224E-5</v>
       </c>
       <c r="R122" s="67">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>1.2847222222222224E-5</v>
       </c>
       <c r="S122" s="67">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>1.2847222222222224E-5</v>
       </c>
       <c r="T122" s="67">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>1.2847222222222224E-5</v>
       </c>
       <c r="U122" s="67">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>1.2847222222222224E-5</v>
       </c>
       <c r="V122" s="67">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>1.2847222222222224E-5</v>
       </c>
       <c r="W122" s="67">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>1.2847222222222224E-5</v>
       </c>
       <c r="X122" s="67"/>
@@ -14462,19 +14462,19 @@
         <v>1.2847222222222224E-5</v>
       </c>
       <c r="Z122" s="67">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0.13875000000000001</v>
       </c>
       <c r="AA122" s="67">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0.13875000000000001</v>
       </c>
       <c r="AB122" s="67">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0.13875000000000001</v>
       </c>
       <c r="AD122" s="1" t="b">
-        <f>M122=AB122</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE122" s="67">
@@ -14566,7 +14566,7 @@
         <v>21600</v>
       </c>
       <c r="AD123" s="1" t="b">
-        <f>M123=AB123</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE123" s="82">
@@ -14658,7 +14658,7 @@
         <v>43200</v>
       </c>
       <c r="AD124" s="1" t="b">
-        <f>M124=AB124</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE124" s="88">
@@ -14750,7 +14750,7 @@
         <v>0.8</v>
       </c>
       <c r="AD125" s="1" t="b">
-        <f>M125=AB125</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE125" s="77">
@@ -14843,7 +14843,7 @@
         <v>2.0833333333333335E-4</v>
       </c>
       <c r="AD126" s="1" t="b">
-        <f>M126=AB126</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE126" s="78">
@@ -14935,7 +14935,7 @@
         <v>5.7899999999999998E-7</v>
       </c>
       <c r="AD127" s="1" t="b">
-        <f>M127=AB127</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE127" s="77">
@@ -15027,7 +15027,7 @@
         <v>2.0833333333333335E-4</v>
       </c>
       <c r="AD128" s="1" t="b">
-        <f>M128=AB128</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE128" s="78">
@@ -15119,7 +15119,7 @@
         <v>0</v>
       </c>
       <c r="AD129" s="1" t="b">
-        <f>M129=AB129</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="AE129" s="78">
@@ -15211,7 +15211,7 @@
         <v>0</v>
       </c>
       <c r="AD130" s="1" t="b">
-        <f>M130=AB130</f>
+        <f t="shared" ref="AD130:AD193" si="63">M130=AB130</f>
         <v>1</v>
       </c>
       <c r="AE130" s="78">
@@ -15246,11 +15246,11 @@
         <v>5.9999999999999997E-7</v>
       </c>
       <c r="I131" s="83">
-        <f t="shared" ref="I131:AF131" si="61">0.0000002*3</f>
+        <f t="shared" ref="I131:AF131" si="64">0.0000002*3</f>
         <v>5.9999999999999997E-7</v>
       </c>
       <c r="J131" s="83">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>5.9999999999999997E-7</v>
       </c>
       <c r="K131" s="83">
@@ -15259,52 +15259,52 @@
       </c>
       <c r="L131" s="83"/>
       <c r="M131" s="83">
-        <f t="shared" ref="M131:Y131" si="62">0.0000002 * 2 / 1000</f>
+        <f t="shared" ref="M131:Y131" si="65">0.0000002 * 2 / 1000</f>
         <v>3.9999999999999996E-10</v>
       </c>
       <c r="N131" s="83">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v>3.9999999999999996E-10</v>
       </c>
       <c r="O131" s="83">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v>3.9999999999999996E-10</v>
       </c>
       <c r="P131" s="83">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v>3.9999999999999996E-10</v>
       </c>
       <c r="Q131" s="83">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v>3.9999999999999996E-10</v>
       </c>
       <c r="R131" s="83">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v>3.9999999999999996E-10</v>
       </c>
       <c r="S131" s="83">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v>3.9999999999999996E-10</v>
       </c>
       <c r="T131" s="83">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v>3.9999999999999996E-10</v>
       </c>
       <c r="U131" s="83">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v>3.9999999999999996E-10</v>
       </c>
       <c r="V131" s="83">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v>3.9999999999999996E-10</v>
       </c>
       <c r="W131" s="83">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v>3.9999999999999996E-10</v>
       </c>
       <c r="X131" s="83"/>
       <c r="Y131" s="83">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v>3.9999999999999996E-10</v>
       </c>
       <c r="Z131" s="83">
@@ -15323,15 +15323,15 @@
         <v>4.0000000000000001E-8</v>
       </c>
       <c r="AD131" s="1" t="b">
-        <f>M131=AB131</f>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="AE131" s="83">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>5.9999999999999997E-7</v>
       </c>
       <c r="AF131" s="83">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>5.9999999999999997E-7</v>
       </c>
     </row>
@@ -15356,93 +15356,93 @@
       </c>
       <c r="G132" s="71"/>
       <c r="H132" s="83">
-        <f t="shared" ref="H132:AF132" si="63">1000 * 0.000001 / 12</f>
+        <f t="shared" ref="H132:AF132" si="66">1000 * 0.000001 / 12</f>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="I132" s="83">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="J132" s="83">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="K132" s="83">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="L132" s="83"/>
       <c r="M132" s="83">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="N132" s="83">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="O132" s="83">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="P132" s="83">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="Q132" s="83">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="R132" s="83">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="S132" s="83">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="T132" s="83">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="U132" s="83">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="V132" s="83">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="W132" s="83">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="X132" s="83"/>
       <c r="Y132" s="83">
+        <f t="shared" si="66"/>
+        <v>8.3333333333333331E-5</v>
+      </c>
+      <c r="Z132" s="83">
+        <f t="shared" si="66"/>
+        <v>8.3333333333333331E-5</v>
+      </c>
+      <c r="AA132" s="83">
+        <f t="shared" si="66"/>
+        <v>8.3333333333333331E-5</v>
+      </c>
+      <c r="AB132" s="83">
+        <f t="shared" si="66"/>
+        <v>8.3333333333333331E-5</v>
+      </c>
+      <c r="AD132" s="1" t="b">
         <f t="shared" si="63"/>
+        <v>1</v>
+      </c>
+      <c r="AE132" s="83">
+        <f t="shared" si="66"/>
         <v>8.3333333333333331E-5</v>
       </c>
-      <c r="Z132" s="83">
-        <f t="shared" si="63"/>
-        <v>8.3333333333333331E-5</v>
-      </c>
-      <c r="AA132" s="83">
-        <f t="shared" si="63"/>
-        <v>8.3333333333333331E-5</v>
-      </c>
-      <c r="AB132" s="83">
-        <f t="shared" si="63"/>
-        <v>8.3333333333333331E-5</v>
-      </c>
-      <c r="AD132" s="1" t="b">
-        <f>M132=AB132</f>
-        <v>1</v>
-      </c>
-      <c r="AE132" s="83">
-        <f t="shared" si="63"/>
-        <v>8.3333333333333331E-5</v>
-      </c>
       <c r="AF132" s="83">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v>8.3333333333333331E-5</v>
       </c>
     </row>
@@ -15528,7 +15528,7 @@
         <v>524</v>
       </c>
       <c r="AD133" s="1" t="b">
-        <f>M133=AB133</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE133" s="89" t="s">
@@ -15575,11 +15575,11 @@
       </c>
       <c r="L134" s="83"/>
       <c r="M134" s="83">
-        <f t="shared" ref="M134:Y134" si="64">0.0005 / 10</f>
+        <f t="shared" ref="M134:Y134" si="67">0.0005 / 10</f>
         <v>5.0000000000000002E-5</v>
       </c>
       <c r="N134" s="83">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>5.0000000000000002E-5</v>
       </c>
       <c r="O134" s="83">
@@ -15587,40 +15587,40 @@
         <v>5.0000000000000001E-4</v>
       </c>
       <c r="P134" s="83">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>5.0000000000000002E-5</v>
       </c>
       <c r="Q134" s="83">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>5.0000000000000002E-5</v>
       </c>
       <c r="R134" s="83">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>5.0000000000000002E-5</v>
       </c>
       <c r="S134" s="83">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>5.0000000000000002E-5</v>
       </c>
       <c r="T134" s="83">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>5.0000000000000002E-5</v>
       </c>
       <c r="U134" s="83">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>5.0000000000000002E-5</v>
       </c>
       <c r="V134" s="83">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>5.0000000000000002E-5</v>
       </c>
       <c r="W134" s="83">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>5.0000000000000002E-5</v>
       </c>
       <c r="X134" s="83"/>
       <c r="Y134" s="83">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>5.0000000000000002E-5</v>
       </c>
       <c r="Z134" s="83">
@@ -15640,7 +15640,7 @@
         <v>5.9999999999999995E-4</v>
       </c>
       <c r="AD134" s="1" t="b">
-        <f>M134=AB134</f>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="AE134" s="83">
@@ -15732,7 +15732,7 @@
         <v>4.9999999999999999E-13</v>
       </c>
       <c r="AD135" s="1" t="b">
-        <f>M135=AB135</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE135" s="83">
@@ -15824,7 +15824,7 @@
         <v>10</v>
       </c>
       <c r="AD136" s="1" t="b">
-        <f>M136=AB136</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE136" s="77">
@@ -15916,7 +15916,7 @@
         <v>-0.04</v>
       </c>
       <c r="AD137" s="1" t="b">
-        <f>M137=AB137</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE137" s="77">
@@ -16008,7 +16008,7 @@
         <v>2.9</v>
       </c>
       <c r="AD138" s="1" t="b">
-        <f>M138=AB138</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE138" s="77">
@@ -16100,7 +16100,7 @@
         <v>1</v>
       </c>
       <c r="AD139" s="1" t="b">
-        <f>M139=AB139</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE139" s="77">
@@ -16147,52 +16147,52 @@
       </c>
       <c r="L140" s="80"/>
       <c r="M140" s="80">
-        <f t="shared" ref="M140:Y140" si="65">0.0000002 * 2 / 10</f>
+        <f t="shared" ref="M140:Y140" si="68">0.0000002 * 2 / 10</f>
         <v>4.0000000000000001E-8</v>
       </c>
       <c r="N140" s="80">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>4.0000000000000001E-8</v>
       </c>
       <c r="O140" s="80">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>4.0000000000000001E-8</v>
       </c>
       <c r="P140" s="80">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>4.0000000000000001E-8</v>
       </c>
       <c r="Q140" s="80">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>4.0000000000000001E-8</v>
       </c>
       <c r="R140" s="80">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>4.0000000000000001E-8</v>
       </c>
       <c r="S140" s="80">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>4.0000000000000001E-8</v>
       </c>
       <c r="T140" s="80">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>4.0000000000000001E-8</v>
       </c>
       <c r="U140" s="80">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>4.0000000000000001E-8</v>
       </c>
       <c r="V140" s="80">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>4.0000000000000001E-8</v>
       </c>
       <c r="W140" s="80">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>4.0000000000000001E-8</v>
       </c>
       <c r="X140" s="80"/>
       <c r="Y140" s="80">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>4.0000000000000001E-8</v>
       </c>
       <c r="Z140" s="80">
@@ -16211,7 +16211,7 @@
         <v>4.0000000000000001E-8</v>
       </c>
       <c r="AD140" s="1" t="b">
-        <f>M140=AB140</f>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="AE140" s="80">
@@ -16303,7 +16303,7 @@
         <v>10</v>
       </c>
       <c r="AD141" s="1" t="b">
-        <f>M141=AB141</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE141" s="77">
@@ -16395,7 +16395,7 @@
         <v>-0.04</v>
       </c>
       <c r="AD142" s="1" t="b">
-        <f>M142=AB142</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE142" s="77">
@@ -16487,7 +16487,7 @@
         <v>2.9</v>
       </c>
       <c r="AD143" s="1" t="b">
-        <f>M143=AB143</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE143" s="77">
@@ -16579,7 +16579,7 @@
         <v>1</v>
       </c>
       <c r="AD144" s="1" t="b">
-        <f>M144=AB144</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE144" s="77">
@@ -16671,7 +16671,7 @@
         <v>0</v>
       </c>
       <c r="AD145" s="1" t="b">
-        <f>M145=AB145</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE145" s="77">
@@ -16763,7 +16763,7 @@
         <v>5.0000000000000004E-6</v>
       </c>
       <c r="AD146" s="1" t="b">
-        <f>M146=AB146</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE146" s="80">
@@ -16855,7 +16855,7 @@
         <v>0</v>
       </c>
       <c r="AD147" s="1" t="b">
-        <f>M147=AB147</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE147" s="77">
@@ -16947,7 +16947,7 @@
         <v>2E-3</v>
       </c>
       <c r="AD148" s="1" t="b">
-        <f>M148=AB148</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE148" s="77">
@@ -17039,7 +17039,7 @@
         <v>3.9999999999999998E-6</v>
       </c>
       <c r="AD149" s="1" t="b">
-        <f>M149=AB149</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE149" s="80">
@@ -17131,7 +17131,7 @@
         <v>3.7699999999999999E-10</v>
       </c>
       <c r="AD150" s="1" t="b">
-        <f>M150=AB150</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE150" s="80">
@@ -17223,7 +17223,7 @@
         <v>20</v>
       </c>
       <c r="AD151" s="1" t="b">
-        <f>M151=AB151</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE151" s="77">
@@ -17315,7 +17315,7 @@
         <v>-0.06</v>
       </c>
       <c r="AD152" s="1" t="b">
-        <f>M152=AB152</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE152" s="77">
@@ -17407,7 +17407,7 @@
         <v>0.89100000000000001</v>
       </c>
       <c r="AD153" s="1" t="b">
-        <f>M153=AB153</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE153" s="77">
@@ -17499,7 +17499,7 @@
         <v>1</v>
       </c>
       <c r="AD154" s="1" t="b">
-        <f>M154=AB154</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE154" s="77">
@@ -17591,7 +17591,7 @@
         <v>4.0000000000000003E-5</v>
       </c>
       <c r="AD155" s="1" t="b">
-        <f>M155=AB155</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE155" s="80">
@@ -17683,7 +17683,7 @@
         <v>5.8333333333333335E-9</v>
       </c>
       <c r="AD156" s="1" t="b">
-        <f>M156=AB156</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE156" s="80">
@@ -17775,7 +17775,7 @@
         <v>20</v>
       </c>
       <c r="AD157" s="1" t="b">
-        <f>M157=AB157</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE157" s="77">
@@ -17867,7 +17867,7 @@
         <v>-0.06</v>
       </c>
       <c r="AD158" s="1" t="b">
-        <f>M158=AB158</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE158" s="77">
@@ -17959,7 +17959,7 @@
         <v>0.89100000000000001</v>
       </c>
       <c r="AD159" s="1" t="b">
-        <f>M159=AB159</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE159" s="77">
@@ -18051,7 +18051,7 @@
         <v>1</v>
       </c>
       <c r="AD160" s="1" t="b">
-        <f>M160=AB160</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE160" s="77">
@@ -18143,7 +18143,7 @@
         <v>4.0000000000000003E-5</v>
       </c>
       <c r="AD161" s="1" t="b">
-        <f>M161=AB161</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE161" s="80">
@@ -18235,7 +18235,7 @@
         <v>4.0000000000000001E-8</v>
       </c>
       <c r="AD162" s="1" t="b">
-        <f>M162=AB162</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE162" s="83">
@@ -18327,7 +18327,7 @@
         <v>20</v>
       </c>
       <c r="AD163" s="1" t="b">
-        <f>M163=AB163</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE163" s="77">
@@ -18419,7 +18419,7 @@
         <v>-4.4200000000000003E-2</v>
       </c>
       <c r="AD164" s="1" t="b">
-        <f>M164=AB164</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE164" s="77">
@@ -18511,7 +18511,7 @@
         <v>1.55</v>
       </c>
       <c r="AD165" s="1" t="b">
-        <f>M165=AB165</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE165" s="77">
@@ -18603,7 +18603,7 @@
         <v>1</v>
       </c>
       <c r="AD166" s="1" t="b">
-        <f>M166=AB166</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE166" s="77">
@@ -18695,7 +18695,7 @@
         <v>2.7799999999999998E-4</v>
       </c>
       <c r="AD167" s="1" t="b">
-        <f>M167=AB167</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE167" s="77">
@@ -18787,7 +18787,7 @@
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="AD168" s="1" t="b">
-        <f>M168=AB168</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE168" s="84">
@@ -18879,7 +18879,7 @@
         <v>20</v>
       </c>
       <c r="AD169" s="1" t="b">
-        <f>M169=AB169</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE169" s="77">
@@ -18971,7 +18971,7 @@
         <v>0</v>
       </c>
       <c r="AD170" s="1" t="b">
-        <f>M170=AB170</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE170" s="77">
@@ -19063,7 +19063,7 @@
         <v>1</v>
       </c>
       <c r="AD171" s="1" t="b">
-        <f>M171=AB171</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE171" s="77">
@@ -19155,7 +19155,7 @@
         <v>0</v>
       </c>
       <c r="AD172" s="1" t="b">
-        <f>M172=AB172</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE172" s="77">
@@ -19247,7 +19247,7 @@
         <v>0.4</v>
       </c>
       <c r="AD173" s="1" t="b">
-        <f>M173=AB173</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE173" s="77">
@@ -19339,7 +19339,7 @@
         <v>2.0000000000000001E-9</v>
       </c>
       <c r="AD174" s="1" t="b">
-        <f>M174=AB174</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE174" s="86">
@@ -19431,7 +19431,7 @@
         <v>25</v>
       </c>
       <c r="AD175" s="1" t="b">
-        <f>M175=AB175</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE175" s="77">
@@ -19523,7 +19523,7 @@
         <v>0</v>
       </c>
       <c r="AD176" s="1" t="b">
-        <f>M176=AB176</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE176" s="77">
@@ -19615,7 +19615,7 @@
         <v>3.98</v>
       </c>
       <c r="AD177" s="1" t="b">
-        <f>M177=AB177</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE177" s="77">
@@ -19707,7 +19707,7 @@
         <v>1</v>
       </c>
       <c r="AD178" s="1" t="b">
-        <f>M178=AB178</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE178" s="77">
@@ -19799,7 +19799,7 @@
         <v>1.6666666666666666E-4</v>
       </c>
       <c r="AD179" s="1" t="b">
-        <f>M179=AB179</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE179" s="78">
@@ -19891,7 +19891,7 @@
         <v>1E-8</v>
       </c>
       <c r="AD180" s="1" t="b">
-        <f>M180=AB180</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE180" s="80">
@@ -19983,7 +19983,7 @@
         <v>20</v>
       </c>
       <c r="AD181" s="1" t="b">
-        <f>M181=AB181</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE181" s="77">
@@ -20075,7 +20075,7 @@
         <v>0</v>
       </c>
       <c r="AD182" s="1" t="b">
-        <f>M182=AB182</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE182" s="77">
@@ -20167,7 +20167,7 @@
         <v>2</v>
       </c>
       <c r="AD183" s="1" t="b">
-        <f>M183=AB183</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE183" s="77">
@@ -20259,7 +20259,7 @@
         <v>1</v>
       </c>
       <c r="AD184" s="1" t="b">
-        <f>M184=AB184</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE184" s="77">
@@ -20351,7 +20351,7 @@
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="AD185" s="1" t="b">
-        <f>M185=AB185</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE185" s="78">
@@ -20443,7 +20443,7 @@
         <v>1</v>
       </c>
       <c r="AD186" s="1" t="b">
-        <f>M186=AB186</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE186" s="77">
@@ -20535,7 +20535,7 @@
         <v>2.3533050791148899E-8</v>
       </c>
       <c r="AD187" s="1" t="b">
-        <f>M187=AB187</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE187" s="77">
@@ -20627,7 +20627,7 @@
         <v>20</v>
       </c>
       <c r="AD188" s="1" t="b">
-        <f>M188=AB188</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE188" s="77">
@@ -20719,7 +20719,7 @@
         <v>-0.187</v>
       </c>
       <c r="AD189" s="1" t="b">
-        <f>M189=AB189</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE189" s="77">
@@ -20811,7 +20811,7 @@
         <v>2.48</v>
       </c>
       <c r="AD190" s="1" t="b">
-        <f>M190=AB190</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE190" s="77">
@@ -20903,7 +20903,7 @@
         <v>1</v>
       </c>
       <c r="AD191" s="1" t="b">
-        <f>M191=AB191</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE191" s="77">
@@ -20995,7 +20995,7 @@
         <v>6.1060227588121015E-4</v>
       </c>
       <c r="AD192" s="1" t="b">
-        <f>M192=AB192</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE192" s="77">
@@ -21087,7 +21087,7 @@
         <v>3.9999999999999998E-7</v>
       </c>
       <c r="AD193" s="1" t="b">
-        <f>M193=AB193</f>
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
       <c r="AE193" s="85">
@@ -21179,7 +21179,7 @@
         <v>25</v>
       </c>
       <c r="AD194" s="1" t="b">
-        <f>M194=AB194</f>
+        <f t="shared" ref="AD194:AD225" si="69">M194=AB194</f>
         <v>1</v>
       </c>
       <c r="AE194" s="77">
@@ -21271,7 +21271,7 @@
         <v>0</v>
       </c>
       <c r="AD195" s="1" t="b">
-        <f>M195=AB195</f>
+        <f t="shared" si="69"/>
         <v>1</v>
       </c>
       <c r="AE195" s="77">
@@ -21363,7 +21363,7 @@
         <v>3.98</v>
       </c>
       <c r="AD196" s="1" t="b">
-        <f>M196=AB196</f>
+        <f t="shared" si="69"/>
         <v>1</v>
       </c>
       <c r="AE196" s="77">
@@ -21455,7 +21455,7 @@
         <v>1</v>
       </c>
       <c r="AD197" s="1" t="b">
-        <f>M197=AB197</f>
+        <f t="shared" si="69"/>
         <v>1</v>
       </c>
       <c r="AE197" s="77">
@@ -21547,7 +21547,7 @@
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="AD198" s="1" t="b">
-        <f>M198=AB198</f>
+        <f t="shared" si="69"/>
         <v>1</v>
       </c>
       <c r="AE198" s="78">
@@ -21639,7 +21639,7 @@
         <v>3.9999999999999998E-7</v>
       </c>
       <c r="AD199" s="1" t="b">
-        <f>M199=AB199</f>
+        <f t="shared" si="69"/>
         <v>1</v>
       </c>
       <c r="AE199" s="85">
@@ -21731,7 +21731,7 @@
         <v>25</v>
       </c>
       <c r="AD200" s="1" t="b">
-        <f>M200=AB200</f>
+        <f t="shared" si="69"/>
         <v>1</v>
       </c>
       <c r="AE200" s="77">
@@ -21823,7 +21823,7 @@
         <v>0</v>
       </c>
       <c r="AD201" s="1" t="b">
-        <f>M201=AB201</f>
+        <f t="shared" si="69"/>
         <v>1</v>
       </c>
       <c r="AE201" s="77">
@@ -21915,7 +21915,7 @@
         <v>3.98</v>
       </c>
       <c r="AD202" s="1" t="b">
-        <f>M202=AB202</f>
+        <f t="shared" si="69"/>
         <v>1</v>
       </c>
       <c r="AE202" s="77">
@@ -22007,7 +22007,7 @@
         <v>1</v>
       </c>
       <c r="AD203" s="1" t="b">
-        <f>M203=AB203</f>
+        <f t="shared" si="69"/>
         <v>1</v>
       </c>
       <c r="AE203" s="77">
@@ -22099,7 +22099,7 @@
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="AD204" s="1" t="b">
-        <f>M204=AB204</f>
+        <f t="shared" si="69"/>
         <v>1</v>
       </c>
       <c r="AE204" s="78">
@@ -22191,7 +22191,7 @@
         <v>1.9999999999999999E-7</v>
       </c>
       <c r="AD205" s="1" t="b">
-        <f>M205=AB205</f>
+        <f t="shared" si="69"/>
         <v>1</v>
       </c>
       <c r="AE205" s="85">
@@ -22283,7 +22283,7 @@
         <v>25</v>
       </c>
       <c r="AD206" s="1" t="b">
-        <f>M206=AB206</f>
+        <f t="shared" si="69"/>
         <v>1</v>
       </c>
       <c r="AE206" s="77">
@@ -22375,7 +22375,7 @@
         <v>0</v>
       </c>
       <c r="AD207" s="1" t="b">
-        <f>M207=AB207</f>
+        <f t="shared" si="69"/>
         <v>1</v>
       </c>
       <c r="AE207" s="77">
@@ -22467,7 +22467,7 @@
         <v>3.98</v>
       </c>
       <c r="AD208" s="1" t="b">
-        <f>M208=AB208</f>
+        <f t="shared" si="69"/>
         <v>1</v>
       </c>
       <c r="AE208" s="77">
@@ -22559,7 +22559,7 @@
         <v>1</v>
       </c>
       <c r="AD209" s="1" t="b">
-        <f>M209=AB209</f>
+        <f t="shared" si="69"/>
         <v>1</v>
       </c>
       <c r="AE209" s="77">
@@ -22651,7 +22651,7 @@
         <v>8.3333333333333331E-5</v>
       </c>
       <c r="AD210" s="1" t="b">
-        <f>M210=AB210</f>
+        <f t="shared" si="69"/>
         <v>1</v>
       </c>
       <c r="AE210" s="78">
@@ -22743,7 +22743,7 @@
         <v>90</v>
       </c>
       <c r="AD211" s="1" t="b">
-        <f>M211=AB211</f>
+        <f t="shared" si="69"/>
         <v>1</v>
       </c>
       <c r="AE211" s="95" t="s">
@@ -22776,15 +22776,15 @@
         <v>0.5</v>
       </c>
       <c r="H212" s="83">
-        <f t="shared" ref="H212:J212" si="66">0.00002</f>
+        <f t="shared" ref="H212:J212" si="70">0.00002</f>
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="I212" s="83">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="J212" s="83">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="K212" s="83">
@@ -22855,7 +22855,7 @@
       </c>
       <c r="AC212" s="1"/>
       <c r="AD212" s="1" t="b">
-        <f>M212=AB212</f>
+        <f t="shared" si="69"/>
         <v>1</v>
       </c>
       <c r="AE212" s="2">
@@ -22948,7 +22948,7 @@
       </c>
       <c r="AC213" s="1"/>
       <c r="AD213" s="1" t="b">
-        <f>M213=AB213</f>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="AE213" s="99">
@@ -22981,85 +22981,85 @@
         <v>0.5</v>
       </c>
       <c r="H214" s="83">
-        <f t="shared" ref="H214:AB214" si="67">0.00002 / 14</f>
+        <f t="shared" ref="H214:AB214" si="71">0.00002 / 14</f>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="I214" s="83">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="J214" s="83">
         <v>2E-3</v>
       </c>
       <c r="K214" s="83">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="L214" s="83"/>
       <c r="M214" s="83">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="N214" s="83">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="O214" s="83">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="P214" s="83">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="Q214" s="83">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="R214" s="83">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="S214" s="83">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="T214" s="83">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="U214" s="83">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="V214" s="83">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="W214" s="83">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="X214" s="83"/>
       <c r="Y214" s="83">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="Z214" s="83">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="AA214" s="83">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="AB214" s="83">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>1.4285714285714286E-6</v>
       </c>
       <c r="AC214" s="1"/>
       <c r="AD214" s="1" t="b">
-        <f>M214=AB214</f>
+        <f t="shared" si="69"/>
         <v>1</v>
       </c>
       <c r="AE214" s="100">
@@ -23152,7 +23152,7 @@
       </c>
       <c r="AC215" s="1"/>
       <c r="AD215" s="1" t="b">
-        <f>M215=AB215</f>
+        <f t="shared" si="69"/>
         <v>1</v>
       </c>
       <c r="AE215" s="98">
@@ -23245,7 +23245,7 @@
       </c>
       <c r="AC216" s="1"/>
       <c r="AD216" s="1" t="b">
-        <f>M216=AB216</f>
+        <f t="shared" si="69"/>
         <v>1</v>
       </c>
       <c r="AE216" s="98">
@@ -23338,7 +23338,7 @@
       </c>
       <c r="AC217" s="1"/>
       <c r="AD217" s="1" t="b">
-        <f>M217=AB217</f>
+        <f t="shared" si="69"/>
         <v>1</v>
       </c>
       <c r="AE217" s="98">
@@ -23372,85 +23372,85 @@
         <v>1.2499999999999999E-6</v>
       </c>
       <c r="H218" s="99">
-        <f t="shared" ref="H218:AB218" si="68">1250*0.000001/5</f>
+        <f t="shared" ref="H218:AB218" si="72">1250*0.000001/5</f>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="I218" s="99">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="J218" s="99">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="K218" s="99">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="L218" s="99"/>
       <c r="M218" s="99">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="N218" s="99">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="O218" s="99">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="P218" s="99">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="Q218" s="99">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="R218" s="99">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="S218" s="99">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="T218" s="99">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="U218" s="99">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="V218" s="99">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="W218" s="99">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="X218" s="99"/>
       <c r="Y218" s="99">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="Z218" s="99">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="AA218" s="99">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="AB218" s="99">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="AD218" s="1" t="b">
-        <f>M218=AB218</f>
+        <f t="shared" si="69"/>
         <v>1</v>
       </c>
       <c r="AE218" s="99">
@@ -23542,7 +23542,7 @@
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="AD219" s="1" t="b">
-        <f>M219=AB219</f>
+        <f t="shared" si="69"/>
         <v>1</v>
       </c>
       <c r="AE219" s="99">
@@ -23602,40 +23602,40 @@
         <v>2.4999999999999998E-11</v>
       </c>
       <c r="P220" s="83">
-        <f t="shared" ref="P220:Y220" si="69" xml:space="preserve"> 0.0000000000025</f>
+        <f t="shared" ref="P220:Y220" si="73" xml:space="preserve"> 0.0000000000025</f>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="Q220" s="83">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="R220" s="83">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="S220" s="83">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="T220" s="83">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="U220" s="83">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="V220" s="83">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="W220" s="83">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="X220" s="83"/>
       <c r="Y220" s="83">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="Z220" s="83">
@@ -23651,7 +23651,7 @@
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="AD220" s="1" t="b">
-        <f>M220=AB220</f>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
     </row>
@@ -23695,52 +23695,52 @@
       </c>
       <c r="L221" s="83"/>
       <c r="M221" s="83">
-        <f>0.00000000005 *2</f>
-        <v>1E-10</v>
+        <f>0.00000000005 *2 / 100</f>
+        <v>9.9999999999999998E-13</v>
       </c>
       <c r="N221" s="83">
-        <f>0.00000000005 *2</f>
-        <v>1E-10</v>
+        <f>0.00000000005 *2 / 100</f>
+        <v>9.9999999999999998E-13</v>
       </c>
       <c r="O221" s="83">
         <f>0.00000000005 *2</f>
         <v>1E-10</v>
       </c>
       <c r="P221" s="83">
-        <f t="shared" ref="P221:Y221" si="70">0.00000000005 / 10 / 8</f>
+        <f t="shared" ref="P221:Y221" si="74">0.00000000005 / 10 / 8</f>
         <v>6.2500000000000006E-13</v>
       </c>
       <c r="Q221" s="83">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>6.2500000000000006E-13</v>
       </c>
       <c r="R221" s="83">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>6.2500000000000006E-13</v>
       </c>
       <c r="S221" s="83">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>6.2500000000000006E-13</v>
       </c>
       <c r="T221" s="83">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>6.2500000000000006E-13</v>
       </c>
       <c r="U221" s="83">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>6.2500000000000006E-13</v>
       </c>
       <c r="V221" s="83">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>6.2500000000000006E-13</v>
       </c>
       <c r="W221" s="83">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>6.2500000000000006E-13</v>
       </c>
       <c r="X221" s="83"/>
       <c r="Y221" s="83">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>6.2500000000000006E-13</v>
       </c>
       <c r="Z221" s="83">
@@ -23756,7 +23756,7 @@
         <v>5.0000000000000002E-11</v>
       </c>
       <c r="AD221" s="1" t="b">
-        <f>M221=AB221</f>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
     </row>
@@ -23791,49 +23791,51 @@
       </c>
       <c r="L222" s="83"/>
       <c r="M222" s="83">
-        <v>0</v>
+        <f>0.0000001 * 10 /2 / 100</f>
+        <v>5.0000000000000001E-9</v>
       </c>
       <c r="N222" s="83">
-        <v>0</v>
+        <f>0.0000001 * 10 /2 / 100 /2</f>
+        <v>2.5000000000000001E-9</v>
       </c>
       <c r="O222" s="83">
         <v>0</v>
       </c>
       <c r="P222" s="83">
-        <f t="shared" ref="P222:Y222" si="71">0.0000001 / 2</f>
+        <f t="shared" ref="P222:Y222" si="75">0.0000001 / 2</f>
         <v>4.9999999999999998E-8</v>
       </c>
       <c r="Q222" s="83">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>4.9999999999999998E-8</v>
       </c>
       <c r="R222" s="83">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>4.9999999999999998E-8</v>
       </c>
       <c r="S222" s="83">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>4.9999999999999998E-8</v>
       </c>
       <c r="T222" s="83">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>4.9999999999999998E-8</v>
       </c>
       <c r="U222" s="83">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>4.9999999999999998E-8</v>
       </c>
       <c r="V222" s="83">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>4.9999999999999998E-8</v>
       </c>
       <c r="W222" s="83">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>4.9999999999999998E-8</v>
       </c>
       <c r="X222" s="83"/>
       <c r="Y222" s="83">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>4.9999999999999998E-8</v>
       </c>
       <c r="Z222" s="83">
@@ -23849,7 +23851,7 @@
         <v>4.9999999999999998E-7</v>
       </c>
       <c r="AD222" s="1" t="b">
-        <f>M222=AB222</f>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
     </row>
@@ -23884,12 +23886,10 @@
       </c>
       <c r="L223" s="83"/>
       <c r="M223" s="83">
-        <f>100</f>
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="N223" s="83">
-        <f>100</f>
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="O223" s="83">
         <f>100</f>
@@ -23945,8 +23945,8 @@
         <v>100</v>
       </c>
       <c r="AD223" s="1" t="b">
-        <f>M223=AB223</f>
-        <v>1</v>
+        <f t="shared" si="69"/>
+        <v>0</v>
       </c>
     </row>
     <row r="224" spans="1:32" x14ac:dyDescent="0.25">
@@ -23989,52 +23989,52 @@
       </c>
       <c r="L224" s="83"/>
       <c r="M224" s="83">
-        <f t="shared" ref="M224:Y224" si="72">0.000001 / 10000 / 4 / 10</f>
+        <f t="shared" ref="M224:Y224" si="76">0.000001 / 10000 / 4 / 10</f>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="N224" s="83">
-        <f t="shared" si="72"/>
+        <f t="shared" si="76"/>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="O224" s="83">
-        <f t="shared" si="72"/>
+        <f t="shared" si="76"/>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="P224" s="83">
-        <f t="shared" si="72"/>
+        <f t="shared" si="76"/>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="Q224" s="83">
-        <f t="shared" si="72"/>
+        <f t="shared" si="76"/>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="R224" s="83">
-        <f t="shared" si="72"/>
+        <f t="shared" si="76"/>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="S224" s="83">
-        <f t="shared" si="72"/>
+        <f t="shared" si="76"/>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="T224" s="83">
-        <f t="shared" si="72"/>
+        <f t="shared" si="76"/>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="U224" s="83">
-        <f t="shared" si="72"/>
+        <f t="shared" si="76"/>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="V224" s="83">
-        <f t="shared" si="72"/>
+        <f t="shared" si="76"/>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="W224" s="83">
-        <f t="shared" si="72"/>
+        <f t="shared" si="76"/>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="X224" s="83"/>
       <c r="Y224" s="83">
-        <f t="shared" si="72"/>
+        <f t="shared" si="76"/>
         <v>2.4999999999999998E-12</v>
       </c>
       <c r="Z224" s="83">
@@ -24050,7 +24050,7 @@
         <v>2.4999999999999998E-11</v>
       </c>
       <c r="AD224" s="1" t="b">
-        <f>M224=AB224</f>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
     </row>
@@ -24091,52 +24091,52 @@
       </c>
       <c r="L225" s="83"/>
       <c r="M225" s="83">
-        <f t="shared" ref="M225:Y225" si="73">0.00001</f>
+        <f t="shared" ref="M225:Y225" si="77">0.00001</f>
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="N225" s="83">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="O225" s="83">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="P225" s="83">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="Q225" s="83">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="R225" s="83">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="S225" s="83">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="T225" s="83">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="U225" s="83">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="V225" s="83">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="W225" s="83">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="X225" s="83"/>
       <c r="Y225" s="83">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="Z225" s="83">
@@ -24155,7 +24155,7 @@
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="AD225" s="1" t="b">
-        <f>M225=AB225</f>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
     </row>
@@ -24196,52 +24196,52 @@
       </c>
       <c r="L226" s="83"/>
       <c r="M226" s="83">
-        <f t="shared" ref="M226:Y226" si="74" xml:space="preserve"> 0.001 * 10</f>
+        <f t="shared" ref="M226:Y226" si="78" xml:space="preserve"> 0.001 * 10</f>
         <v>0.01</v>
       </c>
       <c r="N226" s="83">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>0.01</v>
       </c>
       <c r="O226" s="83">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>0.01</v>
       </c>
       <c r="P226" s="83">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>0.01</v>
       </c>
       <c r="Q226" s="83">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>0.01</v>
       </c>
       <c r="R226" s="83">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>0.01</v>
       </c>
       <c r="S226" s="83">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>0.01</v>
       </c>
       <c r="T226" s="83">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>0.01</v>
       </c>
       <c r="U226" s="83">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>0.01</v>
       </c>
       <c r="V226" s="83">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>0.01</v>
       </c>
       <c r="W226" s="83">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>0.01</v>
       </c>
       <c r="X226" s="83"/>
       <c r="Y226" s="83">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>0.01</v>
       </c>
       <c r="Z226" s="83">
@@ -24304,40 +24304,40 @@
         <v>1.2500000000000002E-7</v>
       </c>
       <c r="P227" s="83">
-        <f t="shared" ref="P227:Y227" si="75">0.00001 / 3</f>
+        <f t="shared" ref="P227:Y227" si="79">0.00001 / 3</f>
         <v>3.3333333333333337E-6</v>
       </c>
       <c r="Q227" s="99">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>3.3333333333333337E-6</v>
       </c>
       <c r="R227" s="99">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>3.3333333333333337E-6</v>
       </c>
       <c r="S227" s="99">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>3.3333333333333337E-6</v>
       </c>
       <c r="T227" s="99">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>3.3333333333333337E-6</v>
       </c>
       <c r="U227" s="99">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>3.3333333333333337E-6</v>
       </c>
       <c r="V227" s="99">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>3.3333333333333337E-6</v>
       </c>
       <c r="W227" s="99">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>3.3333333333333337E-6</v>
       </c>
       <c r="X227" s="99"/>
       <c r="Y227" s="99">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>3.3333333333333337E-6</v>
       </c>
       <c r="Z227" s="99">
@@ -24379,85 +24379,85 @@
         <v>0.10886399999999999</v>
       </c>
       <c r="H228" s="83">
-        <f t="shared" ref="H228:AB228" si="76">0.84*(0.36^2)</f>
+        <f t="shared" ref="H228:AB228" si="80">0.84*(0.36^2)</f>
         <v>0.10886399999999999</v>
       </c>
       <c r="I228" s="83">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="J228" s="83">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="K228" s="83">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="L228" s="83"/>
       <c r="M228" s="83">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="N228" s="83">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="O228" s="83">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="P228" s="83">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="Q228" s="83">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="R228" s="83">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="S228" s="83">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="T228" s="83">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="U228" s="83">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="V228" s="83">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="W228" s="83">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="X228" s="83"/>
       <c r="Y228" s="83">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="Z228" s="83">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="AA228" s="83">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="AB228" s="83">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>0.10886399999999999</v>
       </c>
       <c r="AD228" s="1" t="b">
-        <f>M228=AB228</f>
+        <f t="shared" ref="AD228:AD233" si="81">M228=AB228</f>
         <v>1</v>
       </c>
     </row>
@@ -24543,7 +24543,7 @@
         <v>0.2</v>
       </c>
       <c r="AD229" s="1" t="b">
-        <f>M229=AB229</f>
+        <f t="shared" si="81"/>
         <v>1</v>
       </c>
     </row>
@@ -24629,7 +24629,7 @@
         <v>473</v>
       </c>
       <c r="AD230" s="1" t="b">
-        <f>M230=AB230</f>
+        <f t="shared" si="81"/>
         <v>1</v>
       </c>
     </row>
@@ -24657,85 +24657,85 @@
         <v>0.2</v>
       </c>
       <c r="H231" s="83">
-        <f t="shared" ref="H231:AB231" si="77">2*0.1</f>
+        <f t="shared" ref="H231:AB231" si="82">2*0.1</f>
         <v>0.2</v>
       </c>
       <c r="I231" s="83">
-        <f t="shared" si="77"/>
+        <f t="shared" si="82"/>
         <v>0.2</v>
       </c>
       <c r="J231" s="83">
-        <f t="shared" si="77"/>
+        <f t="shared" si="82"/>
         <v>0.2</v>
       </c>
       <c r="K231" s="83">
-        <f t="shared" si="77"/>
+        <f t="shared" si="82"/>
         <v>0.2</v>
       </c>
       <c r="L231" s="83"/>
       <c r="M231" s="83">
-        <f t="shared" si="77"/>
+        <f t="shared" si="82"/>
         <v>0.2</v>
       </c>
       <c r="N231" s="83">
-        <f t="shared" si="77"/>
+        <f t="shared" si="82"/>
         <v>0.2</v>
       </c>
       <c r="O231" s="83">
-        <f t="shared" si="77"/>
+        <f t="shared" si="82"/>
         <v>0.2</v>
       </c>
       <c r="P231" s="83">
-        <f t="shared" si="77"/>
+        <f t="shared" si="82"/>
         <v>0.2</v>
       </c>
       <c r="Q231" s="83">
-        <f t="shared" si="77"/>
+        <f t="shared" si="82"/>
         <v>0.2</v>
       </c>
       <c r="R231" s="83">
-        <f t="shared" si="77"/>
+        <f t="shared" si="82"/>
         <v>0.2</v>
       </c>
       <c r="S231" s="83">
-        <f t="shared" si="77"/>
+        <f t="shared" si="82"/>
         <v>0.2</v>
       </c>
       <c r="T231" s="83">
-        <f t="shared" si="77"/>
+        <f t="shared" si="82"/>
         <v>0.2</v>
       </c>
       <c r="U231" s="83">
-        <f t="shared" si="77"/>
+        <f t="shared" si="82"/>
         <v>0.2</v>
       </c>
       <c r="V231" s="83">
-        <f t="shared" si="77"/>
+        <f t="shared" si="82"/>
         <v>0.2</v>
       </c>
       <c r="W231" s="83">
-        <f t="shared" si="77"/>
+        <f t="shared" si="82"/>
         <v>0.2</v>
       </c>
       <c r="X231" s="83"/>
       <c r="Y231" s="83">
-        <f t="shared" si="77"/>
+        <f t="shared" si="82"/>
         <v>0.2</v>
       </c>
       <c r="Z231" s="83">
-        <f t="shared" si="77"/>
+        <f t="shared" si="82"/>
         <v>0.2</v>
       </c>
       <c r="AA231" s="83">
-        <f t="shared" si="77"/>
+        <f t="shared" si="82"/>
         <v>0.2</v>
       </c>
       <c r="AB231" s="83">
-        <f t="shared" si="77"/>
+        <f t="shared" si="82"/>
         <v>0.2</v>
       </c>
       <c r="AD231" s="1" t="b">
-        <f>M231=AB231</f>
+        <f t="shared" si="81"/>
         <v>1</v>
       </c>
     </row>
@@ -24821,7 +24821,7 @@
         <v>1E-3</v>
       </c>
       <c r="AD232" s="1" t="b">
-        <f>M232=AB232</f>
+        <f t="shared" si="81"/>
         <v>1</v>
       </c>
     </row>
@@ -24870,39 +24870,39 @@
         <v>5.0000000000000004E-6</v>
       </c>
       <c r="O233" s="83">
-        <f t="shared" ref="O233:W233" si="78">0.00001 /2</f>
+        <f t="shared" ref="O233:W233" si="83">0.00001 /2</f>
         <v>5.0000000000000004E-6</v>
       </c>
       <c r="P233" s="83">
-        <f t="shared" si="78"/>
+        <f t="shared" si="83"/>
         <v>5.0000000000000004E-6</v>
       </c>
       <c r="Q233" s="83">
-        <f t="shared" si="78"/>
+        <f t="shared" si="83"/>
         <v>5.0000000000000004E-6</v>
       </c>
       <c r="R233" s="83">
-        <f t="shared" si="78"/>
+        <f t="shared" si="83"/>
         <v>5.0000000000000004E-6</v>
       </c>
       <c r="S233" s="83">
-        <f t="shared" si="78"/>
+        <f t="shared" si="83"/>
         <v>5.0000000000000004E-6</v>
       </c>
       <c r="T233" s="83">
-        <f t="shared" si="78"/>
+        <f t="shared" si="83"/>
         <v>5.0000000000000004E-6</v>
       </c>
       <c r="U233" s="83">
-        <f t="shared" si="78"/>
+        <f t="shared" si="83"/>
         <v>5.0000000000000004E-6</v>
       </c>
       <c r="V233" s="83">
-        <f t="shared" si="78"/>
+        <f t="shared" si="83"/>
         <v>5.0000000000000004E-6</v>
       </c>
       <c r="W233" s="83">
-        <f t="shared" si="78"/>
+        <f t="shared" si="83"/>
         <v>5.0000000000000004E-6</v>
       </c>
       <c r="X233" s="83"/>
@@ -24927,7 +24927,7 @@
         <v>5.0000000000000004E-6</v>
       </c>
       <c r="AD233" s="1" t="b">
-        <f>M233=AB233</f>
+        <f t="shared" si="81"/>
         <v>1</v>
       </c>
     </row>
@@ -24968,52 +24968,52 @@
       </c>
       <c r="L234" s="83"/>
       <c r="M234" s="83">
-        <f t="shared" ref="M234:Y234" si="79">0.000000005 / 5</f>
+        <f t="shared" ref="M234:Y234" si="84">0.000000005 / 5</f>
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="N234" s="83">
-        <f t="shared" si="79"/>
+        <f t="shared" si="84"/>
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="O234" s="83">
-        <f t="shared" si="79"/>
+        <f t="shared" si="84"/>
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="P234" s="83">
-        <f t="shared" si="79"/>
+        <f t="shared" si="84"/>
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="Q234" s="83">
-        <f t="shared" si="79"/>
+        <f t="shared" si="84"/>
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="R234" s="83">
-        <f t="shared" si="79"/>
+        <f t="shared" si="84"/>
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="S234" s="83">
-        <f t="shared" si="79"/>
+        <f t="shared" si="84"/>
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="T234" s="83">
-        <f t="shared" si="79"/>
+        <f t="shared" si="84"/>
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="U234" s="83">
-        <f t="shared" si="79"/>
+        <f t="shared" si="84"/>
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="V234" s="83">
-        <f t="shared" si="79"/>
+        <f t="shared" si="84"/>
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="W234" s="83">
-        <f t="shared" si="79"/>
+        <f t="shared" si="84"/>
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="X234" s="83"/>
       <c r="Y234" s="83">
-        <f t="shared" si="79"/>
+        <f t="shared" si="84"/>
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="Z234" s="83">
@@ -25049,18 +25049,18 @@
         <v>550</v>
       </c>
       <c r="G235" s="83">
-        <f t="shared" ref="G235:J235" si="80">0.00002 / 14 / 5</f>
+        <f t="shared" ref="G235:J235" si="85">0.00002 / 14 / 5</f>
         <v>2.8571428571428575E-7</v>
       </c>
       <c r="H235" s="83">
-        <f t="shared" si="80"/>
+        <f t="shared" si="85"/>
         <v>2.8571428571428575E-7</v>
       </c>
       <c r="I235" s="83">
         <v>0</v>
       </c>
       <c r="J235" s="83">
-        <f t="shared" si="80"/>
+        <f t="shared" si="85"/>
         <v>2.8571428571428575E-7</v>
       </c>
       <c r="K235" s="83">
@@ -25138,23 +25138,23 @@
         <v>550</v>
       </c>
       <c r="G236" s="83">
-        <f t="shared" ref="G236:AB236" si="81">0.00002 / 14 / 5 /10</f>
+        <f t="shared" ref="G236:AB236" si="86">0.00002 / 14 / 5 /10</f>
         <v>2.8571428571428575E-8</v>
       </c>
       <c r="H236" s="83">
-        <f t="shared" si="81"/>
+        <f t="shared" si="86"/>
         <v>2.8571428571428575E-8</v>
       </c>
       <c r="I236" s="83">
-        <f t="shared" si="81"/>
+        <f t="shared" si="86"/>
         <v>2.8571428571428575E-8</v>
       </c>
       <c r="J236" s="83">
-        <f t="shared" si="81"/>
+        <f t="shared" si="86"/>
         <v>2.8571428571428575E-8</v>
       </c>
       <c r="K236" s="83">
-        <f t="shared" si="81"/>
+        <f t="shared" si="86"/>
         <v>2.8571428571428575E-8</v>
       </c>
       <c r="L236" s="83"/>
@@ -25202,7 +25202,7 @@
         <v>0</v>
       </c>
       <c r="AB236" s="83">
-        <f t="shared" si="81"/>
+        <f t="shared" si="86"/>
         <v>2.8571428571428575E-8</v>
       </c>
       <c r="AD236" s="1" t="b">
@@ -25223,6 +25223,282 @@
       </colorScale>
     </cfRule>
     <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G236:AB236">
+    <cfRule type="colorScale" priority="396">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="397">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H129:AB130">
+    <cfRule type="colorScale" priority="400">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H212:AB212">
+    <cfRule type="colorScale" priority="403">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="402">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H213:AB213">
+    <cfRule type="colorScale" priority="406">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="407">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H214:AB214">
+    <cfRule type="colorScale" priority="411">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="410">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H215:AB215">
+    <cfRule type="colorScale" priority="415">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="414">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H216:AB216">
+    <cfRule type="colorScale" priority="419">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="418">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H217:AB217">
+    <cfRule type="colorScale" priority="423">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="422">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H220:AB220">
+    <cfRule type="colorScale" priority="427">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="426">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H221:AB223">
+    <cfRule type="colorScale" priority="431">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="430">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H224:AB224">
+    <cfRule type="colorScale" priority="435">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="434">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H228:AB228">
+    <cfRule type="colorScale" priority="439">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="438">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H229:AB234">
+    <cfRule type="colorScale" priority="442">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="443">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -25277,512 +25553,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB225:AC225 AB226 H225:AA226">
-    <cfRule type="colorScale" priority="386">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="387">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE129:AF130">
-    <cfRule type="colorScale" priority="55">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE131:AF131 H131:AC131">
-    <cfRule type="colorScale" priority="299">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="300">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE132:AF132 H132:AB132">
-    <cfRule type="colorScale" priority="303">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="304">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE134:AF134 H134:AC134">
-    <cfRule type="colorScale" priority="307">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="308">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE135:AF135 H135:AB135">
-    <cfRule type="colorScale" priority="311">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="312">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE140:AF140 H140:AC140">
-    <cfRule type="colorScale" priority="315">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE146:AF146 H146:AB146">
-    <cfRule type="colorScale" priority="317">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="318">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="319">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE162:AF162 H162:AB162">
-    <cfRule type="colorScale" priority="323">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="324">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="325">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE168:AF168 H168:AB168">
-    <cfRule type="colorScale" priority="329">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="330">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="331">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G236:AB236">
-    <cfRule type="colorScale" priority="396">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="397">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H129:AB130">
-    <cfRule type="colorScale" priority="400">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H212:AB212">
-    <cfRule type="colorScale" priority="402">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="403">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H213:AB213">
-    <cfRule type="colorScale" priority="406">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="407">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H214:AB214">
-    <cfRule type="colorScale" priority="410">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="411">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H215:AB215">
-    <cfRule type="colorScale" priority="414">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="415">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H216:AB216">
-    <cfRule type="colorScale" priority="418">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="419">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H217:AB217">
-    <cfRule type="colorScale" priority="422">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="423">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H220:AB220">
-    <cfRule type="colorScale" priority="426">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="427">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H221:AB223">
-    <cfRule type="colorScale" priority="430">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="431">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H224:AB224">
-    <cfRule type="colorScale" priority="434">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="435">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H228:AB228">
-    <cfRule type="colorScale" priority="438">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="439">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H229:AB234">
-    <cfRule type="colorScale" priority="442">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="443">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="M227:P227">
     <cfRule type="colorScale" priority="446">
       <colorScale>
@@ -25827,6 +25597,236 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AB225:AC225 AB226 H225:AA226">
+    <cfRule type="colorScale" priority="386">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="387">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE129:AF130">
+    <cfRule type="colorScale" priority="55">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE131:AF131 H131:AC131">
+    <cfRule type="colorScale" priority="300">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="299">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE132:AF132 H132:AB132">
+    <cfRule type="colorScale" priority="304">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="303">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE134:AF134 H134:AC134">
+    <cfRule type="colorScale" priority="308">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="307">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE135:AF135 H135:AB135">
+    <cfRule type="colorScale" priority="312">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="311">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE140:AF140 H140:AC140">
+    <cfRule type="colorScale" priority="315">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE146:AF146 H146:AB146">
+    <cfRule type="colorScale" priority="319">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="318">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="317">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE162:AF162 H162:AB162">
+    <cfRule type="colorScale" priority="324">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="325">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="323">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE168:AF168 H168:AB168">
+    <cfRule type="colorScale" priority="331">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="330">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="329">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/simulations/scene/inputs/Scenarios_24_11_10.xlsx
+++ b/simulations/scene/inputs/Scenarios_24_11_10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TIGERA~1\AppData\Local\Temp\scp53108\home\torisuten\package\Wheat-BRIDGES\Root_BRIDGES\simulations\scene\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{872D0CDC-96E4-47DC-96C1-54C4EA9DEAF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D73DD3DE-4FD0-41D7-9B70-A05EFBEF2D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2061" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2062" uniqueCount="592">
   <si>
     <t>input_file</t>
   </si>
@@ -3302,6 +3302,9 @@
       <c r="M6" s="36" t="s">
         <v>564</v>
       </c>
+      <c r="N6" s="36" t="s">
+        <v>587</v>
+      </c>
       <c r="O6" s="1" t="e">
         <f>#REF!=M6</f>
         <v>#REF!</v>
